--- a/data/externalStats/File1/RPT_RPT5649048177252MG_externalStats.xlsx
+++ b/data/externalStats/File1/RPT_RPT5649048177252MG_externalStats.xlsx
@@ -2063,7 +2063,7 @@
         <v>1071061</v>
       </c>
       <c r="G25" s="41" t="n">
-        <v>29.40708221676762</v>
+        <v>29.40708221676763</v>
       </c>
       <c r="H25" s="42" t="n">
         <v>24.11919292003513</v>
@@ -2101,7 +2101,7 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>4927825.286071732</v>
+        <v>4892930.933363182</v>
       </c>
       <c r="AI25" s="46" t="n">
         <v>7094.223987863295</v>
@@ -2140,7 +2140,7 @@
         <v>1314049</v>
       </c>
       <c r="G26" s="52" t="n">
-        <v>98.07134749774573</v>
+        <v>98.07134749774571</v>
       </c>
       <c r="H26" s="53" t="n">
         <v>74.05596257889991</v>
@@ -2486,7 +2486,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>179592.8317715834</v>
+        <v>179593.3050163231</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>509.6993712707739</v>
@@ -2568,7 +2568,7 @@
         </is>
       </c>
       <c r="AN31" s="58" t="n">
-        <v>720.9506748454983</v>
+        <v>720.9506748454982</v>
       </c>
       <c r="AW31" s="77" t="n"/>
       <c r="AX31" s="78" t="n"/>
@@ -2620,7 +2620,7 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>142712.7093633255</v>
+        <v>142728.4613732078</v>
       </c>
       <c r="AI32" s="56" t="n">
         <v>1938.318957923954</v>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="AH33" s="122" t="n">
-        <v>122337.3954337065</v>
+        <v>122337.3954337064</v>
       </c>
       <c r="AI33" s="56" t="n">
         <v>358.4698264140781</v>
@@ -2928,7 +2928,7 @@
         </is>
       </c>
       <c r="AH36" s="122" t="n">
-        <v>108001.2805328026</v>
+        <v>105742.4301115444</v>
       </c>
       <c r="AI36" s="56" t="n">
         <v>222.5593240475558</v>
@@ -3005,7 +3005,7 @@
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>77252.62868515062</v>
+        <v>77252.6286851506</v>
       </c>
       <c r="AI37" s="56" t="n">
         <v>278.6758692628373</v>
@@ -3212,7 +3212,7 @@
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>69745.34681762828</v>
+        <v>69746.80722920313</v>
       </c>
       <c r="AI40" s="56" t="n">
         <v>203.9703763401057</v>
@@ -3289,7 +3289,7 @@
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>69529.4815161007</v>
+        <v>69529.48151610068</v>
       </c>
       <c r="AI41" s="56" t="n">
         <v>199.0707660676643</v>
@@ -3523,7 +3523,7 @@
         <v>65717.04599821538</v>
       </c>
       <c r="AI44" s="84" t="n">
-        <v>68.22039641815653</v>
+        <v>68.22039641815654</v>
       </c>
       <c r="AK44" s="126" t="n">
         <v>20</v>
@@ -3694,7 +3694,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>5484218.867007687</v>
+        <v>5449324.514299135</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>12821.12275198584</v>
@@ -3710,7 +3710,7 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>1089329.097041982</v>
+        <v>1089329.570286722</v>
       </c>
       <c r="AH50" s="56" t="n">
         <v>6903.200315204283</v>
@@ -3958,7 +3958,7 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>271672.0299799231</v>
+        <v>269414.271825942</v>
       </c>
       <c r="AH53" s="56" t="n">
         <v>500.4368615867007</v>
@@ -4120,7 +4120,7 @@
         </is>
       </c>
       <c r="AG55" s="122" t="n">
-        <v>172405.0316900854</v>
+        <v>172408.6034545767</v>
       </c>
       <c r="AH55" s="56" t="n">
         <v>500.4178695794146</v>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>152589.5740804524</v>
+        <v>152606.4125685388</v>
       </c>
       <c r="AH56" s="56" t="n">
         <v>2102.862750485375</v>
@@ -4328,7 +4328,7 @@
         <v>0</v>
       </c>
       <c r="Q58" s="131" t="n">
-        <v>7.09762893823543</v>
+        <v>7.097628938235432</v>
       </c>
       <c r="R58" s="131" t="n">
         <v>0</v>
@@ -4337,7 +4337,7 @@
         <v>0</v>
       </c>
       <c r="T58" s="132" t="n">
-        <v>7.09762893823543</v>
+        <v>7.097628938235432</v>
       </c>
       <c r="V58" s="130" t="n">
         <v>0</v>
@@ -4363,7 +4363,7 @@
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>99533.70574482295</v>
+        <v>99535.70745840274</v>
       </c>
       <c r="AH58" s="56" t="n">
         <v>296.8783488091591</v>
@@ -4391,7 +4391,7 @@
         <v>19</v>
       </c>
       <c r="J59" s="130" t="n">
-        <v>24.87719139716618</v>
+        <v>24.87719139716617</v>
       </c>
       <c r="K59" s="131" t="n">
         <v>0</v>
@@ -4403,7 +4403,7 @@
         <v>0.6176590635903295</v>
       </c>
       <c r="N59" s="132" t="n">
-        <v>25.49485046075651</v>
+        <v>25.4948504607565</v>
       </c>
       <c r="P59" s="130" t="n">
         <v>27.65663487526179</v>
@@ -4415,7 +4415,7 @@
         <v>0</v>
       </c>
       <c r="S59" s="131" t="n">
-        <v>0.6107794764899805</v>
+        <v>0.6107794764899804</v>
       </c>
       <c r="T59" s="132" t="n">
         <v>28.26741435175177</v>
@@ -4444,7 +4444,7 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>80589.41309172871</v>
+        <v>80592.0376122811</v>
       </c>
       <c r="AH59" s="56" t="n">
         <v>142.7523736965244</v>
@@ -4487,7 +4487,7 @@
         <v>12.15752497820848</v>
       </c>
       <c r="P60" s="130" t="n">
-        <v>6.618249046619541</v>
+        <v>6.618249046619539</v>
       </c>
       <c r="Q60" s="131" t="n">
         <v>0</v>
@@ -4499,7 +4499,7 @@
         <v>0</v>
       </c>
       <c r="T60" s="132" t="n">
-        <v>6.618249046619541</v>
+        <v>6.618249046619539</v>
       </c>
       <c r="V60" s="130" t="n">
         <v>6.034114128367583</v>
@@ -4525,10 +4525,10 @@
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>74725.20826634043</v>
+        <v>74725.99272474776</v>
       </c>
       <c r="AH60" s="56" t="n">
-        <v>255.6573809308344</v>
+        <v>255.6573809308345</v>
       </c>
     </row>
     <row r="61">
@@ -4553,13 +4553,13 @@
         <v>5271</v>
       </c>
       <c r="J61" s="130" t="n">
-        <v>6044.873869593556</v>
+        <v>6044.873869593554</v>
       </c>
       <c r="K61" s="131" t="n">
-        <v>3778.992897518413</v>
+        <v>3778.992897518414</v>
       </c>
       <c r="L61" s="131" t="n">
-        <v>69.29836851932255</v>
+        <v>69.29836851932257</v>
       </c>
       <c r="M61" s="131" t="n">
         <v>0</v>
@@ -4568,10 +4568,10 @@
         <v>9893.165135631292</v>
       </c>
       <c r="P61" s="130" t="n">
-        <v>6228.776889941023</v>
+        <v>6228.77688994102</v>
       </c>
       <c r="Q61" s="131" t="n">
-        <v>3999.114543167051</v>
+        <v>3999.114543167052</v>
       </c>
       <c r="R61" s="131" t="n">
         <v>73.5852791072068</v>
@@ -4583,7 +4583,7 @@
         <v>10301.47671221528</v>
       </c>
       <c r="V61" s="130" t="n">
-        <v>6447.101264258591</v>
+        <v>6447.101264258589</v>
       </c>
       <c r="W61" s="131" t="n">
         <v>4230.066745339464</v>
@@ -4634,13 +4634,13 @@
         <v>976</v>
       </c>
       <c r="J62" s="130" t="n">
-        <v>351.9287478386029</v>
+        <v>351.9287478386028</v>
       </c>
       <c r="K62" s="131" t="n">
-        <v>695.26532200108</v>
+        <v>695.2653220010801</v>
       </c>
       <c r="L62" s="131" t="n">
-        <v>4.363987808065344</v>
+        <v>4.363987808065345</v>
       </c>
       <c r="M62" s="131" t="n">
         <v>0</v>
@@ -4649,10 +4649,10 @@
         <v>1051.558057647748</v>
       </c>
       <c r="P62" s="130" t="n">
-        <v>344.867797743876</v>
+        <v>344.8677977438759</v>
       </c>
       <c r="Q62" s="131" t="n">
-        <v>695.6708181072372</v>
+        <v>695.6708181072373</v>
       </c>
       <c r="R62" s="131" t="n">
         <v>4.376881306996877</v>
@@ -4664,10 +4664,10 @@
         <v>1044.91549715811</v>
       </c>
       <c r="V62" s="130" t="n">
-        <v>337.2252462051625</v>
+        <v>337.2252462051626</v>
       </c>
       <c r="W62" s="131" t="n">
-        <v>693.7423997998152</v>
+        <v>693.7423997998151</v>
       </c>
       <c r="X62" s="131" t="n">
         <v>4.349920807420687</v>
@@ -4721,7 +4721,7 @@
         <v>2139.409809914607</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>34.42048685206294</v>
+        <v>34.42048685206299</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>4055.662939861252</v>
@@ -4736,10 +4736,10 @@
         <v>2604.953328398544</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>42.03577551248003</v>
+        <v>42.03577551248006</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>4367.592784770584</v>
+        <v>4367.592784770583</v>
       </c>
       <c r="T63" s="132" t="n">
         <v>10176.20914193729</v>
@@ -4748,7 +4748,7 @@
         <v>3718.42453944005</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>3171.189177178967</v>
+        <v>3171.189177178965</v>
       </c>
       <c r="X63" s="131" t="n">
         <v>51.03255827472316</v>
@@ -4768,7 +4768,7 @@
         </is>
       </c>
       <c r="AG63" s="122" t="n">
-        <v>69529.4815161007</v>
+        <v>69529.48151610068</v>
       </c>
       <c r="AH63" s="56" t="n">
         <v>199.0707660676643</v>
@@ -4805,10 +4805,10 @@
         <v>0</v>
       </c>
       <c r="M64" s="134" t="n">
-        <v>4055.659530255102</v>
+        <v>4055.659530255103</v>
       </c>
       <c r="N64" s="135" t="n">
-        <v>4055.659530255102</v>
+        <v>4055.659530255103</v>
       </c>
       <c r="P64" s="133" t="n">
         <v>0</v>
@@ -4820,10 +4820,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>4367.589286582867</v>
+        <v>4367.589286582866</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>4367.589286582867</v>
+        <v>4367.589286582866</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -5060,10 +5060,10 @@
         <v>48404.11294602313</v>
       </c>
       <c r="P67" s="139" t="n">
-        <v>29468.774697933</v>
+        <v>29468.77469793299</v>
       </c>
       <c r="Q67" s="140" t="n">
-        <v>10340.41686575611</v>
+        <v>10340.41686575612</v>
       </c>
       <c r="R67" s="140" t="n">
         <v>142.2558187419964</v>
@@ -5072,19 +5072,19 @@
         <v>529.4434178862319</v>
       </c>
       <c r="T67" s="141" t="n">
-        <v>40480.89080031734</v>
+        <v>40480.89080031733</v>
       </c>
       <c r="V67" s="139" t="n">
         <v>27700.89671012675</v>
       </c>
       <c r="W67" s="140" t="n">
-        <v>8009.429015133594</v>
+        <v>8009.429015133596</v>
       </c>
       <c r="X67" s="140" t="n">
         <v>115.5740789429929</v>
       </c>
       <c r="Y67" s="140" t="n">
-        <v>507.7439456670622</v>
+        <v>507.7439456670623</v>
       </c>
       <c r="Z67" s="141" t="n">
         <v>36333.6437498704</v>
@@ -5126,7 +5126,7 @@
         <v>15292</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>41792.11030289561</v>
+        <v>41792.1103028956</v>
       </c>
       <c r="K68" s="143" t="n">
         <v>21604.37829025543</v>
@@ -5144,16 +5144,16 @@
         <v>39238.32152279546</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>17647.25318436718</v>
+        <v>17647.25318436719</v>
       </c>
       <c r="R68" s="143" t="n">
         <v>262.2537546686801</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>4897.646982133306</v>
+        <v>4897.646982133305</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>66413.0647305475</v>
+        <v>66413.06473054748</v>
       </c>
       <c r="V68" s="142" t="n">
         <v>38240.73362856136</v>
@@ -5182,7 +5182,7 @@
         <v>40941.91924881711</v>
       </c>
       <c r="AH68" s="84" t="n">
-        <v>800.1560408871607</v>
+        <v>800.1560408871605</v>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1" thickBot="1">
@@ -5762,10 +5762,10 @@
         <v>0</v>
       </c>
       <c r="S77" s="131" t="n">
-        <v>0.8356985266883201</v>
+        <v>0.8356985266883199</v>
       </c>
       <c r="T77" s="132" t="n">
-        <v>0.8356985266883201</v>
+        <v>0.8356985266883199</v>
       </c>
       <c r="V77" s="130" t="n">
         <v>0</v>
@@ -5777,10 +5777,10 @@
         <v>0</v>
       </c>
       <c r="Y77" s="131" t="n">
-        <v>0.8963748172115764</v>
+        <v>0.896374817211576</v>
       </c>
       <c r="Z77" s="132" t="n">
-        <v>0.8963748172115764</v>
+        <v>0.896374817211576</v>
       </c>
     </row>
     <row r="78">
@@ -5835,7 +5835,7 @@
         <v>19.96087013213621</v>
       </c>
       <c r="V78" s="130" t="n">
-        <v>22.02775740512094</v>
+        <v>22.02775740512093</v>
       </c>
       <c r="W78" s="131" t="n">
         <v>0</v>
@@ -5847,7 +5847,7 @@
         <v>0</v>
       </c>
       <c r="Z78" s="132" t="n">
-        <v>22.02775740512094</v>
+        <v>22.02775740512093</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1">
@@ -5890,7 +5890,7 @@
         <v>2558.682056625253</v>
       </c>
       <c r="Q79" s="131" t="n">
-        <v>2925.262718709261</v>
+        <v>2925.26271870926</v>
       </c>
       <c r="R79" s="131" t="n">
         <v>12.15252135439121</v>
@@ -5902,10 +5902,10 @@
         <v>5496.097296688905</v>
       </c>
       <c r="V79" s="130" t="n">
-        <v>2611.881295037886</v>
+        <v>2611.881295037884</v>
       </c>
       <c r="W79" s="131" t="n">
-        <v>2984.036659919333</v>
+        <v>2984.036659919334</v>
       </c>
       <c r="X79" s="131" t="n">
         <v>12.40600426369416</v>
@@ -5914,7 +5914,7 @@
         <v>0</v>
       </c>
       <c r="Z79" s="132" t="n">
-        <v>5608.323959220913</v>
+        <v>5608.323959220912</v>
       </c>
     </row>
     <row r="80">
@@ -6030,10 +6030,10 @@
         <v>0</v>
       </c>
       <c r="S81" s="131" t="n">
-        <v>732.1357703742319</v>
+        <v>732.1357703742317</v>
       </c>
       <c r="T81" s="132" t="n">
-        <v>767.7667371008351</v>
+        <v>767.7667371008349</v>
       </c>
       <c r="V81" s="130" t="n">
         <v>53.71684799538343</v>
@@ -6045,10 +6045,10 @@
         <v>0</v>
       </c>
       <c r="Y81" s="131" t="n">
-        <v>880.0595490867238</v>
+        <v>880.0595490867235</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>933.7763970821072</v>
+        <v>933.7763970821069</v>
       </c>
     </row>
     <row r="82">
@@ -6097,10 +6097,10 @@
         <v>0</v>
       </c>
       <c r="S82" s="134" t="n">
-        <v>732.1357703742319</v>
+        <v>732.1357703742317</v>
       </c>
       <c r="T82" s="135" t="n">
-        <v>732.1357703742319</v>
+        <v>732.1357703742317</v>
       </c>
       <c r="V82" s="133" t="n">
         <v>0</v>
@@ -6112,10 +6112,10 @@
         <v>0</v>
       </c>
       <c r="Y82" s="134" t="n">
-        <v>880.0595490867238</v>
+        <v>880.0595490867235</v>
       </c>
       <c r="Z82" s="135" t="n">
-        <v>880.0595490867238</v>
+        <v>880.0595490867235</v>
       </c>
     </row>
     <row r="83">
@@ -6299,7 +6299,7 @@
         <v>252865.283451084</v>
       </c>
       <c r="R85" s="140" t="n">
-        <v>3973.333705512458</v>
+        <v>3973.333705512457</v>
       </c>
       <c r="S85" s="140" t="n">
         <v>0</v>
@@ -6314,7 +6314,7 @@
         <v>256728.376959773</v>
       </c>
       <c r="X85" s="140" t="n">
-        <v>4026.459976202601</v>
+        <v>4026.4599762026</v>
       </c>
       <c r="Y85" s="140" t="n">
         <v>0</v>
@@ -6366,10 +6366,10 @@
         <v>255790.5461697932</v>
       </c>
       <c r="R86" s="143" t="n">
-        <v>3985.486226866849</v>
+        <v>3985.486226866848</v>
       </c>
       <c r="S86" s="143" t="n">
-        <v>732.9714689009203</v>
+        <v>732.9714689009201</v>
       </c>
       <c r="T86" s="144" t="n">
         <v>508354.5390776537</v>
@@ -6381,13 +6381,13 @@
         <v>259712.4136196924</v>
       </c>
       <c r="X86" s="143" t="n">
-        <v>4038.865980466295</v>
+        <v>4038.865980466294</v>
       </c>
       <c r="Y86" s="143" t="n">
-        <v>880.9559239039354</v>
+        <v>880.9559239039351</v>
       </c>
       <c r="Z86" s="144" t="n">
-        <v>516784.425697706</v>
+        <v>516784.4256977059</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" thickBot="1">
@@ -6894,7 +6894,7 @@
         <v>0</v>
       </c>
       <c r="Q94" s="131" t="n">
-        <v>7.09762893823543</v>
+        <v>7.097628938235432</v>
       </c>
       <c r="R94" s="131" t="n">
         <v>0</v>
@@ -6903,7 +6903,7 @@
         <v>0</v>
       </c>
       <c r="T94" s="132" t="n">
-        <v>7.09762893823543</v>
+        <v>7.097628938235432</v>
       </c>
       <c r="V94" s="130" t="n">
         <v>0</v>
@@ -6943,7 +6943,7 @@
         <v>19</v>
       </c>
       <c r="J95" s="130" t="n">
-        <v>24.87719139716618</v>
+        <v>24.87719139716617</v>
       </c>
       <c r="K95" s="131" t="n">
         <v>0</v>
@@ -6955,7 +6955,7 @@
         <v>1.367136085871659</v>
       </c>
       <c r="N95" s="132" t="n">
-        <v>26.24432748303784</v>
+        <v>26.24432748303783</v>
       </c>
       <c r="P95" s="130" t="n">
         <v>27.65663487526179</v>
@@ -6967,7 +6967,7 @@
         <v>0</v>
       </c>
       <c r="S95" s="131" t="n">
-        <v>1.446478003178301</v>
+        <v>1.4464780031783</v>
       </c>
       <c r="T95" s="132" t="n">
         <v>29.10311287844009</v>
@@ -6982,7 +6982,7 @@
         <v>0</v>
       </c>
       <c r="Y95" s="131" t="n">
-        <v>1.539423073904819</v>
+        <v>1.539423073904818</v>
       </c>
       <c r="Z95" s="132" t="n">
         <v>32.59117747634145</v>
@@ -7040,7 +7040,7 @@
         <v>26.57911917875575</v>
       </c>
       <c r="V96" s="130" t="n">
-        <v>28.06187153348852</v>
+        <v>28.06187153348851</v>
       </c>
       <c r="W96" s="131" t="n">
         <v>0</v>
@@ -7052,7 +7052,7 @@
         <v>0</v>
       </c>
       <c r="Z96" s="132" t="n">
-        <v>28.06187153348852</v>
+        <v>28.06187153348851</v>
       </c>
     </row>
     <row r="97">
@@ -7077,10 +7077,10 @@
         <v>9704</v>
       </c>
       <c r="J97" s="130" t="n">
-        <v>8521.815565172985</v>
+        <v>8521.815565172983</v>
       </c>
       <c r="K97" s="131" t="n">
-        <v>6628.085294105205</v>
+        <v>6628.085294105206</v>
       </c>
       <c r="L97" s="131" t="n">
         <v>81.12125915531615</v>
@@ -7092,10 +7092,10 @@
         <v>15231.02211843351</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>8787.458946566276</v>
+        <v>8787.458946566274</v>
       </c>
       <c r="Q97" s="131" t="n">
-        <v>6924.377261876311</v>
+        <v>6924.377261876312</v>
       </c>
       <c r="R97" s="131" t="n">
         <v>85.73780046159801</v>
@@ -7107,7 +7107,7 @@
         <v>15797.57400890418</v>
       </c>
       <c r="V97" s="130" t="n">
-        <v>9058.982559296477</v>
+        <v>9058.982559296473</v>
       </c>
       <c r="W97" s="131" t="n">
         <v>7214.103405258798</v>
@@ -7119,7 +7119,7 @@
         <v>0</v>
       </c>
       <c r="Z97" s="132" t="n">
-        <v>16363.1543764469</v>
+        <v>16363.15437644689</v>
       </c>
     </row>
     <row r="98">
@@ -7144,13 +7144,13 @@
         <v>976</v>
       </c>
       <c r="J98" s="130" t="n">
-        <v>351.9287478386029</v>
+        <v>351.9287478386028</v>
       </c>
       <c r="K98" s="131" t="n">
-        <v>695.26532200108</v>
+        <v>695.2653220010801</v>
       </c>
       <c r="L98" s="131" t="n">
-        <v>4.363987808065344</v>
+        <v>4.363987808065345</v>
       </c>
       <c r="M98" s="131" t="n">
         <v>0</v>
@@ -7159,10 +7159,10 @@
         <v>1051.558057647748</v>
       </c>
       <c r="P98" s="130" t="n">
-        <v>344.867797743876</v>
+        <v>344.8677977438759</v>
       </c>
       <c r="Q98" s="131" t="n">
-        <v>695.6708181072372</v>
+        <v>695.6708181072373</v>
       </c>
       <c r="R98" s="131" t="n">
         <v>4.376881306996877</v>
@@ -7174,10 +7174,10 @@
         <v>1044.91549715811</v>
       </c>
       <c r="V98" s="130" t="n">
-        <v>337.2252462051625</v>
+        <v>337.2252462051626</v>
       </c>
       <c r="W98" s="131" t="n">
-        <v>693.7423997998152</v>
+        <v>693.7423997998151</v>
       </c>
       <c r="X98" s="131" t="n">
         <v>4.349920807420687</v>
@@ -7232,10 +7232,10 @@
         <v>2604.95332839858</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>42.03577551248054</v>
+        <v>42.03577551247963</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>5099.728555144816</v>
+        <v>5099.728555144814</v>
       </c>
       <c r="T99" s="132" t="n">
         <v>10943.97587903814</v>
@@ -7250,7 +7250,7 @@
         <v>51.03255827472276</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>5541.410161234373</v>
+        <v>5541.410161234372</v>
       </c>
       <c r="Z99" s="132" t="n">
         <v>12535.77328412354</v>
@@ -7302,10 +7302,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>5099.725056957099</v>
+        <v>5099.725056957098</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>5099.725056957099</v>
+        <v>5099.725056957098</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -7519,10 +7519,10 @@
         <v>264737.8059749066</v>
       </c>
       <c r="X103" s="140" t="n">
-        <v>4142.034055145594</v>
+        <v>4142.034055145593</v>
       </c>
       <c r="Y103" s="140" t="n">
-        <v>507.7439456670622</v>
+        <v>507.7439456670623</v>
       </c>
       <c r="Z103" s="141" t="n">
         <v>545672.9854099642</v>
@@ -7571,10 +7571,10 @@
         <v>273437.7993541604</v>
       </c>
       <c r="R104" s="143" t="n">
-        <v>4247.739981535529</v>
+        <v>4247.739981535528</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>5630.618451034226</v>
+        <v>5630.618451034225</v>
       </c>
       <c r="T104" s="144" t="n">
         <v>574767.6038082013</v>
@@ -7586,13 +7586,13 @@
         <v>275824.1403448745</v>
       </c>
       <c r="X104" s="143" t="n">
-        <v>4287.484946119356</v>
+        <v>4287.484946119355</v>
       </c>
       <c r="Y104" s="143" t="n">
         <v>6050.69352997534</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>581216.5896308239</v>
+        <v>581216.5896308238</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -8587,7 +8587,7 @@
         <v>1071061</v>
       </c>
       <c r="G25" s="41" t="n">
-        <v>29.40708221676762</v>
+        <v>29.40708221676763</v>
       </c>
       <c r="H25" s="42" t="n">
         <v>24.11919292003513</v>
@@ -8625,7 +8625,7 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>6296679.872439782</v>
+        <v>6251111.142429026</v>
       </c>
       <c r="AI25" s="46" t="n">
         <v>8867.763082677957</v>
@@ -8664,7 +8664,7 @@
         <v>1314049</v>
       </c>
       <c r="G26" s="52" t="n">
-        <v>98.07134749774573</v>
+        <v>98.07134749774571</v>
       </c>
       <c r="H26" s="53" t="n">
         <v>74.05596257889991</v>
@@ -8721,7 +8721,7 @@
         </is>
       </c>
       <c r="AN26" s="58" t="n">
-        <v>7024.586276347051</v>
+        <v>7024.58627634705</v>
       </c>
     </row>
     <row r="27" ht="15" customHeight="1" thickBot="1">
@@ -8779,7 +8779,7 @@
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>634763.5969597775</v>
+        <v>634763.5969597776</v>
       </c>
       <c r="AI27" s="56" t="n">
         <v>926.3552720223383</v>
@@ -9010,7 +9010,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>195601.2984393665</v>
+        <v>195602.2540080712</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>533.1863182989312</v>
@@ -9144,7 +9144,7 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>169442.0044009371</v>
+        <v>169479.2284243546</v>
       </c>
       <c r="AI32" s="56" t="n">
         <v>1986.350501701309</v>
@@ -9375,7 +9375,7 @@
         </is>
       </c>
       <c r="AH35" s="122" t="n">
-        <v>122786.8432488476</v>
+        <v>120428.7733143354</v>
       </c>
       <c r="AI35" s="56" t="n">
         <v>240.5243126846745</v>
@@ -9532,7 +9532,7 @@
         <v>81509.15863828435</v>
       </c>
       <c r="AI37" s="56" t="n">
-        <v>291.5172533184689</v>
+        <v>291.5172533184688</v>
       </c>
       <c r="AK37" s="123" t="n">
         <v>13</v>
@@ -9736,7 +9736,7 @@
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>73163.97307698094</v>
+        <v>73166.72183213674</v>
       </c>
       <c r="AI40" s="56" t="n">
         <v>201.9551490218655</v>
@@ -9813,7 +9813,7 @@
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>72614.31094965678</v>
+        <v>72614.31094965676</v>
       </c>
       <c r="AI41" s="56" t="n">
         <v>147.4175985741262</v>
@@ -9890,7 +9890,7 @@
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>69138.5945039247</v>
+        <v>69144.39120753236</v>
       </c>
       <c r="AI42" s="56" t="n">
         <v>116.7772917320124</v>
@@ -10218,7 +10218,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>6931443.469399558</v>
+        <v>6885874.739388804</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>15281.88969849521</v>
@@ -10234,7 +10234,7 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>1181805.934086261</v>
+        <v>1181806.889654966</v>
       </c>
       <c r="AH50" s="56" t="n">
         <v>7221.299785728896</v>
@@ -10482,7 +10482,7 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>308765.6115758643</v>
+        <v>306409.9699396395</v>
       </c>
       <c r="AH53" s="56" t="n">
         <v>540.8321250539791</v>
@@ -10563,7 +10563,7 @@
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>181169.0015771704</v>
+        <v>181208.7921849003</v>
       </c>
       <c r="AH54" s="56" t="n">
         <v>2154.971689442402</v>
@@ -10725,7 +10725,7 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>154220.981603612</v>
+        <v>154227.7055605296</v>
       </c>
       <c r="AH56" s="56" t="n">
         <v>415.6609932837869</v>
@@ -10852,7 +10852,7 @@
         <v>0</v>
       </c>
       <c r="Q58" s="131" t="n">
-        <v>7.09762893823543</v>
+        <v>7.097628938235432</v>
       </c>
       <c r="R58" s="131" t="n">
         <v>0</v>
@@ -10861,7 +10861,7 @@
         <v>0</v>
       </c>
       <c r="T58" s="132" t="n">
-        <v>7.09762893823543</v>
+        <v>7.097628938235432</v>
       </c>
       <c r="V58" s="130" t="n">
         <v>0</v>
@@ -10887,7 +10887,7 @@
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>104422.0395065061</v>
+        <v>104425.8354361577</v>
       </c>
       <c r="AH58" s="56" t="n">
         <v>293.9451907229246</v>
@@ -10915,7 +10915,7 @@
         <v>19</v>
       </c>
       <c r="J59" s="130" t="n">
-        <v>24.87719139716618</v>
+        <v>24.87719139716617</v>
       </c>
       <c r="K59" s="131" t="n">
         <v>0</v>
@@ -10927,7 +10927,7 @@
         <v>0.6176590635903295</v>
       </c>
       <c r="N59" s="132" t="n">
-        <v>25.49485046075651</v>
+        <v>25.4948504607565</v>
       </c>
       <c r="P59" s="130" t="n">
         <v>27.65663487526179</v>
@@ -10939,7 +10939,7 @@
         <v>0</v>
       </c>
       <c r="S59" s="131" t="n">
-        <v>0.6107794764899805</v>
+        <v>0.6107794764899804</v>
       </c>
       <c r="T59" s="132" t="n">
         <v>28.26741435175177</v>
@@ -10968,7 +10968,7 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>96957.4166217054</v>
+        <v>96963.21332531306</v>
       </c>
       <c r="AH59" s="56" t="n">
         <v>160.9632940089901</v>
@@ -11011,7 +11011,7 @@
         <v>12.15752497820848</v>
       </c>
       <c r="P60" s="130" t="n">
-        <v>6.618249046619541</v>
+        <v>6.618249046619539</v>
       </c>
       <c r="Q60" s="131" t="n">
         <v>0</v>
@@ -11023,7 +11023,7 @@
         <v>0</v>
       </c>
       <c r="T60" s="132" t="n">
-        <v>6.618249046619541</v>
+        <v>6.618249046619539</v>
       </c>
       <c r="V60" s="130" t="n">
         <v>6.034114128367583</v>
@@ -11077,13 +11077,13 @@
         <v>5271</v>
       </c>
       <c r="J61" s="130" t="n">
-        <v>6044.873869593556</v>
+        <v>6044.873869593554</v>
       </c>
       <c r="K61" s="131" t="n">
-        <v>3778.992897518413</v>
+        <v>3778.992897518414</v>
       </c>
       <c r="L61" s="131" t="n">
-        <v>69.29836851932255</v>
+        <v>69.29836851932257</v>
       </c>
       <c r="M61" s="131" t="n">
         <v>0</v>
@@ -11092,10 +11092,10 @@
         <v>9893.165135631292</v>
       </c>
       <c r="P61" s="130" t="n">
-        <v>6228.776889941023</v>
+        <v>6228.77688994102</v>
       </c>
       <c r="Q61" s="131" t="n">
-        <v>3999.114543167051</v>
+        <v>3999.114543167052</v>
       </c>
       <c r="R61" s="131" t="n">
         <v>73.5852791072068</v>
@@ -11107,7 +11107,7 @@
         <v>10301.47671221528</v>
       </c>
       <c r="V61" s="130" t="n">
-        <v>6447.101264258591</v>
+        <v>6447.101264258589</v>
       </c>
       <c r="W61" s="131" t="n">
         <v>4230.066745339464</v>
@@ -11133,7 +11133,7 @@
         <v>79633.72037209972</v>
       </c>
       <c r="AH61" s="56" t="n">
-        <v>212.4573984897525</v>
+        <v>212.4573984897524</v>
       </c>
     </row>
     <row r="62">
@@ -11158,13 +11158,13 @@
         <v>976</v>
       </c>
       <c r="J62" s="130" t="n">
-        <v>351.9287478386029</v>
+        <v>351.9287478386028</v>
       </c>
       <c r="K62" s="131" t="n">
-        <v>695.26532200108</v>
+        <v>695.2653220010801</v>
       </c>
       <c r="L62" s="131" t="n">
-        <v>4.363987808065344</v>
+        <v>4.363987808065345</v>
       </c>
       <c r="M62" s="131" t="n">
         <v>0</v>
@@ -11173,10 +11173,10 @@
         <v>1051.558057647748</v>
       </c>
       <c r="P62" s="130" t="n">
-        <v>344.867797743876</v>
+        <v>344.8677977438759</v>
       </c>
       <c r="Q62" s="131" t="n">
-        <v>695.6708181072372</v>
+        <v>695.6708181072373</v>
       </c>
       <c r="R62" s="131" t="n">
         <v>4.376881306996877</v>
@@ -11188,10 +11188,10 @@
         <v>1044.91549715811</v>
       </c>
       <c r="V62" s="130" t="n">
-        <v>337.2252462051625</v>
+        <v>337.2252462051626</v>
       </c>
       <c r="W62" s="131" t="n">
-        <v>693.7423997998152</v>
+        <v>693.7423997998151</v>
       </c>
       <c r="X62" s="131" t="n">
         <v>4.349920807420687</v>
@@ -11245,7 +11245,7 @@
         <v>2139.409809914607</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>34.42048685206294</v>
+        <v>34.42048685206299</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>4055.662939861252</v>
@@ -11260,10 +11260,10 @@
         <v>2604.953328398544</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>42.03577551248003</v>
+        <v>42.03577551248006</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>4367.592784770584</v>
+        <v>4367.592784770583</v>
       </c>
       <c r="T63" s="132" t="n">
         <v>10176.20914193729</v>
@@ -11272,7 +11272,7 @@
         <v>3718.42453944005</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>3171.189177178967</v>
+        <v>3171.189177178965</v>
       </c>
       <c r="X63" s="131" t="n">
         <v>51.03255827472316</v>
@@ -11329,10 +11329,10 @@
         <v>0</v>
       </c>
       <c r="M64" s="134" t="n">
-        <v>4055.659530255102</v>
+        <v>4055.659530255103</v>
       </c>
       <c r="N64" s="135" t="n">
-        <v>4055.659530255102</v>
+        <v>4055.659530255103</v>
       </c>
       <c r="P64" s="133" t="n">
         <v>0</v>
@@ -11344,10 +11344,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>4367.589286582867</v>
+        <v>4367.589286582866</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>4367.589286582867</v>
+        <v>4367.589286582866</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -11584,10 +11584,10 @@
         <v>48404.11294602313</v>
       </c>
       <c r="P67" s="139" t="n">
-        <v>29468.774697933</v>
+        <v>29468.77469793299</v>
       </c>
       <c r="Q67" s="140" t="n">
-        <v>10340.41686575611</v>
+        <v>10340.41686575612</v>
       </c>
       <c r="R67" s="140" t="n">
         <v>142.2558187419964</v>
@@ -11596,19 +11596,19 @@
         <v>529.4434178862319</v>
       </c>
       <c r="T67" s="141" t="n">
-        <v>40480.89080031734</v>
+        <v>40480.89080031733</v>
       </c>
       <c r="V67" s="139" t="n">
         <v>27700.89671012675</v>
       </c>
       <c r="W67" s="140" t="n">
-        <v>8009.429015133594</v>
+        <v>8009.429015133596</v>
       </c>
       <c r="X67" s="140" t="n">
         <v>115.5740789429929</v>
       </c>
       <c r="Y67" s="140" t="n">
-        <v>507.7439456670622</v>
+        <v>507.7439456670623</v>
       </c>
       <c r="Z67" s="141" t="n">
         <v>36333.6437498704</v>
@@ -11650,7 +11650,7 @@
         <v>15292</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>41792.11030289561</v>
+        <v>41792.1103028956</v>
       </c>
       <c r="K68" s="143" t="n">
         <v>21604.37829025543</v>
@@ -11668,16 +11668,16 @@
         <v>39238.32152279546</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>17647.25318436718</v>
+        <v>17647.25318436719</v>
       </c>
       <c r="R68" s="143" t="n">
         <v>262.2537546686801</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>4897.646982133306</v>
+        <v>4897.646982133305</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>66413.0647305475</v>
+        <v>66413.06473054748</v>
       </c>
       <c r="V68" s="142" t="n">
         <v>38240.73362856136</v>
@@ -12286,10 +12286,10 @@
         <v>0</v>
       </c>
       <c r="S77" s="131" t="n">
-        <v>0.8356985266883201</v>
+        <v>0.8356985266883199</v>
       </c>
       <c r="T77" s="132" t="n">
-        <v>0.8356985266883201</v>
+        <v>0.8356985266883199</v>
       </c>
       <c r="V77" s="130" t="n">
         <v>0</v>
@@ -12301,10 +12301,10 @@
         <v>0</v>
       </c>
       <c r="Y77" s="131" t="n">
-        <v>0.8963748172115764</v>
+        <v>0.896374817211576</v>
       </c>
       <c r="Z77" s="132" t="n">
-        <v>0.8963748172115764</v>
+        <v>0.896374817211576</v>
       </c>
     </row>
     <row r="78">
@@ -12359,7 +12359,7 @@
         <v>19.96087013213621</v>
       </c>
       <c r="V78" s="130" t="n">
-        <v>22.02775740512094</v>
+        <v>22.02775740512093</v>
       </c>
       <c r="W78" s="131" t="n">
         <v>0</v>
@@ -12371,7 +12371,7 @@
         <v>0</v>
       </c>
       <c r="Z78" s="132" t="n">
-        <v>22.02775740512094</v>
+        <v>22.02775740512093</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1">
@@ -12414,7 +12414,7 @@
         <v>2558.682056625253</v>
       </c>
       <c r="Q79" s="131" t="n">
-        <v>2925.262718709261</v>
+        <v>2925.26271870926</v>
       </c>
       <c r="R79" s="131" t="n">
         <v>12.15252135439121</v>
@@ -12426,10 +12426,10 @@
         <v>5496.097296688905</v>
       </c>
       <c r="V79" s="130" t="n">
-        <v>2611.881295037886</v>
+        <v>2611.881295037884</v>
       </c>
       <c r="W79" s="131" t="n">
-        <v>2984.036659919333</v>
+        <v>2984.036659919334</v>
       </c>
       <c r="X79" s="131" t="n">
         <v>12.40600426369416</v>
@@ -12438,7 +12438,7 @@
         <v>0</v>
       </c>
       <c r="Z79" s="132" t="n">
-        <v>5608.323959220913</v>
+        <v>5608.323959220912</v>
       </c>
     </row>
     <row r="80">
@@ -12554,10 +12554,10 @@
         <v>0</v>
       </c>
       <c r="S81" s="131" t="n">
-        <v>732.1357703742319</v>
+        <v>732.1357703742317</v>
       </c>
       <c r="T81" s="132" t="n">
-        <v>767.7667371008351</v>
+        <v>767.7667371008349</v>
       </c>
       <c r="V81" s="130" t="n">
         <v>53.71684799538343</v>
@@ -12569,10 +12569,10 @@
         <v>0</v>
       </c>
       <c r="Y81" s="131" t="n">
-        <v>880.0595490867238</v>
+        <v>880.0595490867235</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>933.7763970821072</v>
+        <v>933.7763970821069</v>
       </c>
     </row>
     <row r="82">
@@ -12621,10 +12621,10 @@
         <v>0</v>
       </c>
       <c r="S82" s="134" t="n">
-        <v>732.1357703742319</v>
+        <v>732.1357703742317</v>
       </c>
       <c r="T82" s="135" t="n">
-        <v>732.1357703742319</v>
+        <v>732.1357703742317</v>
       </c>
       <c r="V82" s="133" t="n">
         <v>0</v>
@@ -12636,10 +12636,10 @@
         <v>0</v>
       </c>
       <c r="Y82" s="134" t="n">
-        <v>880.0595490867238</v>
+        <v>880.0595490867235</v>
       </c>
       <c r="Z82" s="135" t="n">
-        <v>880.0595490867238</v>
+        <v>880.0595490867235</v>
       </c>
     </row>
     <row r="83">
@@ -12823,7 +12823,7 @@
         <v>252865.283451084</v>
       </c>
       <c r="R85" s="140" t="n">
-        <v>3973.333705512458</v>
+        <v>3973.333705512457</v>
       </c>
       <c r="S85" s="140" t="n">
         <v>0</v>
@@ -12838,7 +12838,7 @@
         <v>256728.376959773</v>
       </c>
       <c r="X85" s="140" t="n">
-        <v>4026.459976202601</v>
+        <v>4026.4599762026</v>
       </c>
       <c r="Y85" s="140" t="n">
         <v>0</v>
@@ -12890,10 +12890,10 @@
         <v>255790.5461697932</v>
       </c>
       <c r="R86" s="143" t="n">
-        <v>3985.486226866849</v>
+        <v>3985.486226866848</v>
       </c>
       <c r="S86" s="143" t="n">
-        <v>732.9714689009203</v>
+        <v>732.9714689009201</v>
       </c>
       <c r="T86" s="144" t="n">
         <v>508354.5390776537</v>
@@ -12905,13 +12905,13 @@
         <v>259712.4136196924</v>
       </c>
       <c r="X86" s="143" t="n">
-        <v>4038.865980466295</v>
+        <v>4038.865980466294</v>
       </c>
       <c r="Y86" s="143" t="n">
-        <v>880.9559239039354</v>
+        <v>880.9559239039351</v>
       </c>
       <c r="Z86" s="144" t="n">
-        <v>516784.425697706</v>
+        <v>516784.4256977059</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" thickBot="1">
@@ -13418,7 +13418,7 @@
         <v>0</v>
       </c>
       <c r="Q94" s="131" t="n">
-        <v>7.09762893823543</v>
+        <v>7.097628938235432</v>
       </c>
       <c r="R94" s="131" t="n">
         <v>0</v>
@@ -13427,7 +13427,7 @@
         <v>0</v>
       </c>
       <c r="T94" s="132" t="n">
-        <v>7.09762893823543</v>
+        <v>7.097628938235432</v>
       </c>
       <c r="V94" s="130" t="n">
         <v>0</v>
@@ -13467,7 +13467,7 @@
         <v>19</v>
       </c>
       <c r="J95" s="130" t="n">
-        <v>24.87719139716618</v>
+        <v>24.87719139716617</v>
       </c>
       <c r="K95" s="131" t="n">
         <v>0</v>
@@ -13479,7 +13479,7 @@
         <v>1.367136085871659</v>
       </c>
       <c r="N95" s="132" t="n">
-        <v>26.24432748303784</v>
+        <v>26.24432748303783</v>
       </c>
       <c r="P95" s="130" t="n">
         <v>27.65663487526179</v>
@@ -13491,7 +13491,7 @@
         <v>0</v>
       </c>
       <c r="S95" s="131" t="n">
-        <v>1.446478003178301</v>
+        <v>1.4464780031783</v>
       </c>
       <c r="T95" s="132" t="n">
         <v>29.10311287844009</v>
@@ -13506,7 +13506,7 @@
         <v>0</v>
       </c>
       <c r="Y95" s="131" t="n">
-        <v>1.539423073904819</v>
+        <v>1.539423073904818</v>
       </c>
       <c r="Z95" s="132" t="n">
         <v>32.59117747634145</v>
@@ -13564,7 +13564,7 @@
         <v>26.57911917875575</v>
       </c>
       <c r="V96" s="130" t="n">
-        <v>28.06187153348852</v>
+        <v>28.06187153348851</v>
       </c>
       <c r="W96" s="131" t="n">
         <v>0</v>
@@ -13576,7 +13576,7 @@
         <v>0</v>
       </c>
       <c r="Z96" s="132" t="n">
-        <v>28.06187153348852</v>
+        <v>28.06187153348851</v>
       </c>
     </row>
     <row r="97">
@@ -13601,10 +13601,10 @@
         <v>9704</v>
       </c>
       <c r="J97" s="130" t="n">
-        <v>8521.815565172985</v>
+        <v>8521.815565172983</v>
       </c>
       <c r="K97" s="131" t="n">
-        <v>6628.085294105205</v>
+        <v>6628.085294105206</v>
       </c>
       <c r="L97" s="131" t="n">
         <v>81.12125915531615</v>
@@ -13616,10 +13616,10 @@
         <v>15231.02211843351</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>8787.458946566276</v>
+        <v>8787.458946566274</v>
       </c>
       <c r="Q97" s="131" t="n">
-        <v>6924.377261876311</v>
+        <v>6924.377261876312</v>
       </c>
       <c r="R97" s="131" t="n">
         <v>85.73780046159801</v>
@@ -13631,7 +13631,7 @@
         <v>15797.57400890418</v>
       </c>
       <c r="V97" s="130" t="n">
-        <v>9058.982559296477</v>
+        <v>9058.982559296473</v>
       </c>
       <c r="W97" s="131" t="n">
         <v>7214.103405258798</v>
@@ -13643,7 +13643,7 @@
         <v>0</v>
       </c>
       <c r="Z97" s="132" t="n">
-        <v>16363.1543764469</v>
+        <v>16363.15437644689</v>
       </c>
     </row>
     <row r="98">
@@ -13668,13 +13668,13 @@
         <v>976</v>
       </c>
       <c r="J98" s="130" t="n">
-        <v>351.9287478386029</v>
+        <v>351.9287478386028</v>
       </c>
       <c r="K98" s="131" t="n">
-        <v>695.26532200108</v>
+        <v>695.2653220010801</v>
       </c>
       <c r="L98" s="131" t="n">
-        <v>4.363987808065344</v>
+        <v>4.363987808065345</v>
       </c>
       <c r="M98" s="131" t="n">
         <v>0</v>
@@ -13683,10 +13683,10 @@
         <v>1051.558057647748</v>
       </c>
       <c r="P98" s="130" t="n">
-        <v>344.867797743876</v>
+        <v>344.8677977438759</v>
       </c>
       <c r="Q98" s="131" t="n">
-        <v>695.6708181072372</v>
+        <v>695.6708181072373</v>
       </c>
       <c r="R98" s="131" t="n">
         <v>4.376881306996877</v>
@@ -13698,10 +13698,10 @@
         <v>1044.91549715811</v>
       </c>
       <c r="V98" s="130" t="n">
-        <v>337.2252462051625</v>
+        <v>337.2252462051626</v>
       </c>
       <c r="W98" s="131" t="n">
-        <v>693.7423997998152</v>
+        <v>693.7423997998151</v>
       </c>
       <c r="X98" s="131" t="n">
         <v>4.349920807420687</v>
@@ -13756,10 +13756,10 @@
         <v>2604.95332839858</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>42.03577551248054</v>
+        <v>42.03577551247963</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>5099.728555144816</v>
+        <v>5099.728555144814</v>
       </c>
       <c r="T99" s="132" t="n">
         <v>10943.97587903814</v>
@@ -13774,7 +13774,7 @@
         <v>51.03255827472276</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>5541.410161234373</v>
+        <v>5541.410161234372</v>
       </c>
       <c r="Z99" s="132" t="n">
         <v>12535.77328412354</v>
@@ -13826,10 +13826,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>5099.725056957099</v>
+        <v>5099.725056957098</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>5099.725056957099</v>
+        <v>5099.725056957098</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -14043,10 +14043,10 @@
         <v>264737.8059749066</v>
       </c>
       <c r="X103" s="140" t="n">
-        <v>4142.034055145594</v>
+        <v>4142.034055145593</v>
       </c>
       <c r="Y103" s="140" t="n">
-        <v>507.7439456670622</v>
+        <v>507.7439456670623</v>
       </c>
       <c r="Z103" s="141" t="n">
         <v>545672.9854099642</v>
@@ -14095,10 +14095,10 @@
         <v>273437.7993541604</v>
       </c>
       <c r="R104" s="143" t="n">
-        <v>4247.739981535529</v>
+        <v>4247.739981535528</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>5630.618451034226</v>
+        <v>5630.618451034225</v>
       </c>
       <c r="T104" s="144" t="n">
         <v>574767.6038082013</v>
@@ -14110,13 +14110,13 @@
         <v>275824.1403448745</v>
       </c>
       <c r="X104" s="143" t="n">
-        <v>4287.484946119356</v>
+        <v>4287.484946119355</v>
       </c>
       <c r="Y104" s="143" t="n">
         <v>6050.69352997534</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>581216.5896308239</v>
+        <v>581216.5896308238</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -15111,7 +15111,7 @@
         <v>1071061</v>
       </c>
       <c r="G25" s="41" t="n">
-        <v>29.40708221676762</v>
+        <v>29.40708221676763</v>
       </c>
       <c r="H25" s="42" t="n">
         <v>24.11919292003513</v>
@@ -15149,7 +15149,7 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>7800562.640378888</v>
+        <v>7751805.566195069</v>
       </c>
       <c r="AI25" s="46" t="n">
         <v>10641.30259354557</v>
@@ -15188,7 +15188,7 @@
         <v>1314049</v>
       </c>
       <c r="G26" s="52" t="n">
-        <v>98.07134749774573</v>
+        <v>98.07134749774571</v>
       </c>
       <c r="H26" s="53" t="n">
         <v>74.05596257889991</v>
@@ -15303,7 +15303,7 @@
         </is>
       </c>
       <c r="AH27" s="122" t="n">
-        <v>728342.3037163918</v>
+        <v>728342.3037163917</v>
       </c>
       <c r="AI27" s="56" t="n">
         <v>1028.254351944796</v>
@@ -15457,7 +15457,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>232740.7056095825</v>
+        <v>232740.7056095824</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>212.4125022456222</v>
@@ -15534,7 +15534,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>215434.421041972</v>
+        <v>215435.8497525222</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>557.7555438461457</v>
@@ -15553,7 +15553,7 @@
         </is>
       </c>
       <c r="AN30" s="58" t="n">
-        <v>34.97712223447874</v>
+        <v>34.97712223447873</v>
       </c>
     </row>
     <row r="31">
@@ -15597,7 +15597,7 @@
         </is>
       </c>
       <c r="AH31" s="122" t="n">
-        <v>198621.6259981354</v>
+        <v>198692.1838050455</v>
       </c>
       <c r="AI31" s="56" t="n">
         <v>2035.572267133469</v>
@@ -15616,7 +15616,7 @@
         </is>
       </c>
       <c r="AN31" s="58" t="n">
-        <v>61.78711170375239</v>
+        <v>61.7871117037524</v>
       </c>
       <c r="AW31" s="77" t="n"/>
       <c r="AX31" s="78" t="n"/>
@@ -15822,10 +15822,10 @@
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>141528.853100419</v>
+        <v>139069.4066315507</v>
       </c>
       <c r="AI34" s="56" t="n">
-        <v>259.2755881015718</v>
+        <v>259.2755881015717</v>
       </c>
       <c r="AK34" s="123" t="n">
         <v>10</v>
@@ -15902,7 +15902,7 @@
         <v>138614.8865263913</v>
       </c>
       <c r="AI35" s="56" t="n">
-        <v>48.16329992778643</v>
+        <v>48.16329992778642</v>
       </c>
       <c r="AK35" s="123" t="n">
         <v>11</v>
@@ -15979,7 +15979,7 @@
         <v>123881.0795628932</v>
       </c>
       <c r="AI36" s="56" t="n">
-        <v>430.1207812819064</v>
+        <v>430.1207812819065</v>
       </c>
       <c r="AK36" s="123" t="n">
         <v>12</v>
@@ -16130,7 +16130,7 @@
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>84158.24574711424</v>
+        <v>84168.98660304653</v>
       </c>
       <c r="AI38" s="56" t="n">
         <v>131.4141574777028</v>
@@ -16193,7 +16193,7 @@
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>77590.73220499986</v>
+        <v>77595.17294414854</v>
       </c>
       <c r="AI39" s="56" t="n">
         <v>199.9598321495294</v>
@@ -16414,7 +16414,7 @@
         </is>
       </c>
       <c r="AH42" s="122" t="n">
-        <v>67285.62855146726</v>
+        <v>67286.40026732098</v>
       </c>
       <c r="AI42" s="56" t="n">
         <v>65.9429241414402</v>
@@ -16491,10 +16491,10 @@
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>67270.80184550273</v>
+        <v>67270.80184550272</v>
       </c>
       <c r="AI43" s="56" t="n">
-        <v>62.16008509289814</v>
+        <v>62.16008509289813</v>
       </c>
       <c r="AK43" s="123" t="n">
         <v>19</v>
@@ -16742,7 +16742,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>8528904.94409528</v>
+        <v>8480147.86991146</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>17760.98313710272</v>
@@ -16758,7 +16758,7 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>1210719.956868905</v>
+        <v>1210721.385579455</v>
       </c>
       <c r="AH50" s="56" t="n">
         <v>6356.681979750578</v>
@@ -17006,7 +17006,7 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>354180.0450142385</v>
+        <v>351725.0475507301</v>
       </c>
       <c r="AH53" s="56" t="n">
         <v>582.9953975231873</v>
@@ -17087,7 +17087,7 @@
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>212368.5520790416</v>
+        <v>212443.9720813232</v>
       </c>
       <c r="AH54" s="56" t="n">
         <v>2208.371887906786</v>
@@ -17249,7 +17249,7 @@
         </is>
       </c>
       <c r="AG56" s="122" t="n">
-        <v>167735.8100830162</v>
+        <v>167746.7557622799</v>
       </c>
       <c r="AH56" s="56" t="n">
         <v>411.0858053593449</v>
@@ -17376,7 +17376,7 @@
         <v>0</v>
       </c>
       <c r="Q58" s="131" t="n">
-        <v>7.09762893823543</v>
+        <v>7.097628938235432</v>
       </c>
       <c r="R58" s="131" t="n">
         <v>0</v>
@@ -17385,7 +17385,7 @@
         <v>0</v>
       </c>
       <c r="T58" s="132" t="n">
-        <v>7.09762893823543</v>
+        <v>7.097628938235432</v>
       </c>
       <c r="V58" s="130" t="n">
         <v>0</v>
@@ -17411,7 +17411,7 @@
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>117275.4377137489</v>
+        <v>117286.1785696812</v>
       </c>
       <c r="AH58" s="56" t="n">
         <v>181.1384332800769</v>
@@ -17439,7 +17439,7 @@
         <v>19</v>
       </c>
       <c r="J59" s="130" t="n">
-        <v>24.87719139716618</v>
+        <v>24.87719139716617</v>
       </c>
       <c r="K59" s="131" t="n">
         <v>0</v>
@@ -17451,7 +17451,7 @@
         <v>0.6176590635903295</v>
       </c>
       <c r="N59" s="132" t="n">
-        <v>25.49485046075651</v>
+        <v>25.4948504607565</v>
       </c>
       <c r="P59" s="130" t="n">
         <v>27.65663487526179</v>
@@ -17463,7 +17463,7 @@
         <v>0</v>
       </c>
       <c r="S59" s="131" t="n">
-        <v>0.6107794764899805</v>
+        <v>0.6107794764899804</v>
       </c>
       <c r="T59" s="132" t="n">
         <v>28.26741435175177</v>
@@ -17535,7 +17535,7 @@
         <v>12.15752497820848</v>
       </c>
       <c r="P60" s="130" t="n">
-        <v>6.618249046619541</v>
+        <v>6.618249046619539</v>
       </c>
       <c r="Q60" s="131" t="n">
         <v>0</v>
@@ -17547,7 +17547,7 @@
         <v>0</v>
       </c>
       <c r="T60" s="132" t="n">
-        <v>6.618249046619541</v>
+        <v>6.618249046619539</v>
       </c>
       <c r="V60" s="130" t="n">
         <v>6.034114128367583</v>
@@ -17573,7 +17573,7 @@
         </is>
       </c>
       <c r="AG60" s="122" t="n">
-        <v>110729.8183557163</v>
+        <v>110735.9686150908</v>
       </c>
       <c r="AH60" s="56" t="n">
         <v>291.0410122385821</v>
@@ -17601,13 +17601,13 @@
         <v>5271</v>
       </c>
       <c r="J61" s="130" t="n">
-        <v>6044.873869593556</v>
+        <v>6044.873869593554</v>
       </c>
       <c r="K61" s="131" t="n">
-        <v>3778.992897518413</v>
+        <v>3778.992897518414</v>
       </c>
       <c r="L61" s="131" t="n">
-        <v>69.29836851932255</v>
+        <v>69.29836851932257</v>
       </c>
       <c r="M61" s="131" t="n">
         <v>0</v>
@@ -17616,10 +17616,10 @@
         <v>9893.165135631292</v>
       </c>
       <c r="P61" s="130" t="n">
-        <v>6228.776889941023</v>
+        <v>6228.77688994102</v>
       </c>
       <c r="Q61" s="131" t="n">
-        <v>3999.114543167051</v>
+        <v>3999.114543167052</v>
       </c>
       <c r="R61" s="131" t="n">
         <v>73.5852791072068</v>
@@ -17631,7 +17631,7 @@
         <v>10301.47671221528</v>
       </c>
       <c r="V61" s="130" t="n">
-        <v>6447.101264258591</v>
+        <v>6447.101264258589</v>
       </c>
       <c r="W61" s="131" t="n">
         <v>4230.066745339464</v>
@@ -17682,13 +17682,13 @@
         <v>976</v>
       </c>
       <c r="J62" s="130" t="n">
-        <v>351.9287478386029</v>
+        <v>351.9287478386028</v>
       </c>
       <c r="K62" s="131" t="n">
-        <v>695.26532200108</v>
+        <v>695.2653220010801</v>
       </c>
       <c r="L62" s="131" t="n">
-        <v>4.363987808065344</v>
+        <v>4.363987808065345</v>
       </c>
       <c r="M62" s="131" t="n">
         <v>0</v>
@@ -17697,10 +17697,10 @@
         <v>1051.558057647748</v>
       </c>
       <c r="P62" s="130" t="n">
-        <v>344.867797743876</v>
+        <v>344.8677977438759</v>
       </c>
       <c r="Q62" s="131" t="n">
-        <v>695.6708181072372</v>
+        <v>695.6708181072373</v>
       </c>
       <c r="R62" s="131" t="n">
         <v>4.376881306996877</v>
@@ -17712,10 +17712,10 @@
         <v>1044.91549715811</v>
       </c>
       <c r="V62" s="130" t="n">
-        <v>337.2252462051625</v>
+        <v>337.2252462051626</v>
       </c>
       <c r="W62" s="131" t="n">
-        <v>693.7423997998152</v>
+        <v>693.7423997998151</v>
       </c>
       <c r="X62" s="131" t="n">
         <v>4.349920807420687</v>
@@ -17769,7 +17769,7 @@
         <v>2139.409809914607</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>34.42048685206294</v>
+        <v>34.42048685206299</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>4055.662939861252</v>
@@ -17784,10 +17784,10 @@
         <v>2604.953328398544</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>42.03577551248003</v>
+        <v>42.03577551248006</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>4367.592784770584</v>
+        <v>4367.592784770583</v>
       </c>
       <c r="T63" s="132" t="n">
         <v>10176.20914193729</v>
@@ -17796,7 +17796,7 @@
         <v>3718.42453944005</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>3171.189177178967</v>
+        <v>3171.189177178965</v>
       </c>
       <c r="X63" s="131" t="n">
         <v>51.03255827472316</v>
@@ -17853,10 +17853,10 @@
         <v>0</v>
       </c>
       <c r="M64" s="134" t="n">
-        <v>4055.659530255102</v>
+        <v>4055.659530255103</v>
       </c>
       <c r="N64" s="135" t="n">
-        <v>4055.659530255102</v>
+        <v>4055.659530255103</v>
       </c>
       <c r="P64" s="133" t="n">
         <v>0</v>
@@ -17868,10 +17868,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>4367.589286582867</v>
+        <v>4367.589286582866</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>4367.589286582867</v>
+        <v>4367.589286582866</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -18108,10 +18108,10 @@
         <v>48404.11294602313</v>
       </c>
       <c r="P67" s="139" t="n">
-        <v>29468.774697933</v>
+        <v>29468.77469793299</v>
       </c>
       <c r="Q67" s="140" t="n">
-        <v>10340.41686575611</v>
+        <v>10340.41686575612</v>
       </c>
       <c r="R67" s="140" t="n">
         <v>142.2558187419964</v>
@@ -18120,19 +18120,19 @@
         <v>529.4434178862319</v>
       </c>
       <c r="T67" s="141" t="n">
-        <v>40480.89080031734</v>
+        <v>40480.89080031733</v>
       </c>
       <c r="V67" s="139" t="n">
         <v>27700.89671012675</v>
       </c>
       <c r="W67" s="140" t="n">
-        <v>8009.429015133594</v>
+        <v>8009.429015133596</v>
       </c>
       <c r="X67" s="140" t="n">
         <v>115.5740789429929</v>
       </c>
       <c r="Y67" s="140" t="n">
-        <v>507.7439456670622</v>
+        <v>507.7439456670623</v>
       </c>
       <c r="Z67" s="141" t="n">
         <v>36333.6437498704</v>
@@ -18146,7 +18146,7 @@
         </is>
       </c>
       <c r="AG67" s="122" t="n">
-        <v>36553.12063732999</v>
+        <v>36554.73731701937</v>
       </c>
       <c r="AH67" s="56" t="n">
         <v>63.56123947609334</v>
@@ -18174,7 +18174,7 @@
         <v>15292</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>41792.11030289561</v>
+        <v>41792.1103028956</v>
       </c>
       <c r="K68" s="143" t="n">
         <v>21604.37829025543</v>
@@ -18192,16 +18192,16 @@
         <v>39238.32152279546</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>17647.25318436718</v>
+        <v>17647.25318436719</v>
       </c>
       <c r="R68" s="143" t="n">
         <v>262.2537546686801</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>4897.646982133306</v>
+        <v>4897.646982133305</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>66413.0647305475</v>
+        <v>66413.06473054748</v>
       </c>
       <c r="V68" s="142" t="n">
         <v>38240.73362856136</v>
@@ -18810,10 +18810,10 @@
         <v>0</v>
       </c>
       <c r="S77" s="131" t="n">
-        <v>0.8356985266883201</v>
+        <v>0.8356985266883199</v>
       </c>
       <c r="T77" s="132" t="n">
-        <v>0.8356985266883201</v>
+        <v>0.8356985266883199</v>
       </c>
       <c r="V77" s="130" t="n">
         <v>0</v>
@@ -18825,10 +18825,10 @@
         <v>0</v>
       </c>
       <c r="Y77" s="131" t="n">
-        <v>0.8963748172115764</v>
+        <v>0.896374817211576</v>
       </c>
       <c r="Z77" s="132" t="n">
-        <v>0.8963748172115764</v>
+        <v>0.896374817211576</v>
       </c>
     </row>
     <row r="78">
@@ -18883,7 +18883,7 @@
         <v>19.96087013213621</v>
       </c>
       <c r="V78" s="130" t="n">
-        <v>22.02775740512094</v>
+        <v>22.02775740512093</v>
       </c>
       <c r="W78" s="131" t="n">
         <v>0</v>
@@ -18895,7 +18895,7 @@
         <v>0</v>
       </c>
       <c r="Z78" s="132" t="n">
-        <v>22.02775740512094</v>
+        <v>22.02775740512093</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1">
@@ -18938,7 +18938,7 @@
         <v>2558.682056625253</v>
       </c>
       <c r="Q79" s="131" t="n">
-        <v>2925.262718709261</v>
+        <v>2925.26271870926</v>
       </c>
       <c r="R79" s="131" t="n">
         <v>12.15252135439121</v>
@@ -18950,10 +18950,10 @@
         <v>5496.097296688905</v>
       </c>
       <c r="V79" s="130" t="n">
-        <v>2611.881295037886</v>
+        <v>2611.881295037884</v>
       </c>
       <c r="W79" s="131" t="n">
-        <v>2984.036659919333</v>
+        <v>2984.036659919334</v>
       </c>
       <c r="X79" s="131" t="n">
         <v>12.40600426369416</v>
@@ -18962,7 +18962,7 @@
         <v>0</v>
       </c>
       <c r="Z79" s="132" t="n">
-        <v>5608.323959220913</v>
+        <v>5608.323959220912</v>
       </c>
     </row>
     <row r="80">
@@ -19078,10 +19078,10 @@
         <v>0</v>
       </c>
       <c r="S81" s="131" t="n">
-        <v>732.1357703742319</v>
+        <v>732.1357703742317</v>
       </c>
       <c r="T81" s="132" t="n">
-        <v>767.7667371008351</v>
+        <v>767.7667371008349</v>
       </c>
       <c r="V81" s="130" t="n">
         <v>53.71684799538343</v>
@@ -19093,10 +19093,10 @@
         <v>0</v>
       </c>
       <c r="Y81" s="131" t="n">
-        <v>880.0595490867238</v>
+        <v>880.0595490867235</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>933.7763970821072</v>
+        <v>933.7763970821069</v>
       </c>
     </row>
     <row r="82">
@@ -19145,10 +19145,10 @@
         <v>0</v>
       </c>
       <c r="S82" s="134" t="n">
-        <v>732.1357703742319</v>
+        <v>732.1357703742317</v>
       </c>
       <c r="T82" s="135" t="n">
-        <v>732.1357703742319</v>
+        <v>732.1357703742317</v>
       </c>
       <c r="V82" s="133" t="n">
         <v>0</v>
@@ -19160,10 +19160,10 @@
         <v>0</v>
       </c>
       <c r="Y82" s="134" t="n">
-        <v>880.0595490867238</v>
+        <v>880.0595490867235</v>
       </c>
       <c r="Z82" s="135" t="n">
-        <v>880.0595490867238</v>
+        <v>880.0595490867235</v>
       </c>
     </row>
     <row r="83">
@@ -19347,7 +19347,7 @@
         <v>252865.283451084</v>
       </c>
       <c r="R85" s="140" t="n">
-        <v>3973.333705512458</v>
+        <v>3973.333705512457</v>
       </c>
       <c r="S85" s="140" t="n">
         <v>0</v>
@@ -19362,7 +19362,7 @@
         <v>256728.376959773</v>
       </c>
       <c r="X85" s="140" t="n">
-        <v>4026.459976202601</v>
+        <v>4026.4599762026</v>
       </c>
       <c r="Y85" s="140" t="n">
         <v>0</v>
@@ -19414,10 +19414,10 @@
         <v>255790.5461697932</v>
       </c>
       <c r="R86" s="143" t="n">
-        <v>3985.486226866849</v>
+        <v>3985.486226866848</v>
       </c>
       <c r="S86" s="143" t="n">
-        <v>732.9714689009203</v>
+        <v>732.9714689009201</v>
       </c>
       <c r="T86" s="144" t="n">
         <v>508354.5390776537</v>
@@ -19429,13 +19429,13 @@
         <v>259712.4136196924</v>
       </c>
       <c r="X86" s="143" t="n">
-        <v>4038.865980466295</v>
+        <v>4038.865980466294</v>
       </c>
       <c r="Y86" s="143" t="n">
-        <v>880.9559239039354</v>
+        <v>880.9559239039351</v>
       </c>
       <c r="Z86" s="144" t="n">
-        <v>516784.425697706</v>
+        <v>516784.4256977059</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" thickBot="1">
@@ -19942,7 +19942,7 @@
         <v>0</v>
       </c>
       <c r="Q94" s="131" t="n">
-        <v>7.09762893823543</v>
+        <v>7.097628938235432</v>
       </c>
       <c r="R94" s="131" t="n">
         <v>0</v>
@@ -19951,7 +19951,7 @@
         <v>0</v>
       </c>
       <c r="T94" s="132" t="n">
-        <v>7.09762893823543</v>
+        <v>7.097628938235432</v>
       </c>
       <c r="V94" s="130" t="n">
         <v>0</v>
@@ -19991,7 +19991,7 @@
         <v>19</v>
       </c>
       <c r="J95" s="130" t="n">
-        <v>24.87719139716618</v>
+        <v>24.87719139716617</v>
       </c>
       <c r="K95" s="131" t="n">
         <v>0</v>
@@ -20003,7 +20003,7 @@
         <v>1.367136085871659</v>
       </c>
       <c r="N95" s="132" t="n">
-        <v>26.24432748303784</v>
+        <v>26.24432748303783</v>
       </c>
       <c r="P95" s="130" t="n">
         <v>27.65663487526179</v>
@@ -20015,7 +20015,7 @@
         <v>0</v>
       </c>
       <c r="S95" s="131" t="n">
-        <v>1.446478003178301</v>
+        <v>1.4464780031783</v>
       </c>
       <c r="T95" s="132" t="n">
         <v>29.10311287844009</v>
@@ -20030,7 +20030,7 @@
         <v>0</v>
       </c>
       <c r="Y95" s="131" t="n">
-        <v>1.539423073904819</v>
+        <v>1.539423073904818</v>
       </c>
       <c r="Z95" s="132" t="n">
         <v>32.59117747634145</v>
@@ -20088,7 +20088,7 @@
         <v>26.57911917875575</v>
       </c>
       <c r="V96" s="130" t="n">
-        <v>28.06187153348852</v>
+        <v>28.06187153348851</v>
       </c>
       <c r="W96" s="131" t="n">
         <v>0</v>
@@ -20100,7 +20100,7 @@
         <v>0</v>
       </c>
       <c r="Z96" s="132" t="n">
-        <v>28.06187153348852</v>
+        <v>28.06187153348851</v>
       </c>
     </row>
     <row r="97">
@@ -20125,10 +20125,10 @@
         <v>9704</v>
       </c>
       <c r="J97" s="130" t="n">
-        <v>8521.815565172985</v>
+        <v>8521.815565172983</v>
       </c>
       <c r="K97" s="131" t="n">
-        <v>6628.085294105205</v>
+        <v>6628.085294105206</v>
       </c>
       <c r="L97" s="131" t="n">
         <v>81.12125915531615</v>
@@ -20140,10 +20140,10 @@
         <v>15231.02211843351</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>8787.458946566276</v>
+        <v>8787.458946566274</v>
       </c>
       <c r="Q97" s="131" t="n">
-        <v>6924.377261876311</v>
+        <v>6924.377261876312</v>
       </c>
       <c r="R97" s="131" t="n">
         <v>85.73780046159801</v>
@@ -20155,7 +20155,7 @@
         <v>15797.57400890418</v>
       </c>
       <c r="V97" s="130" t="n">
-        <v>9058.982559296477</v>
+        <v>9058.982559296473</v>
       </c>
       <c r="W97" s="131" t="n">
         <v>7214.103405258798</v>
@@ -20167,7 +20167,7 @@
         <v>0</v>
       </c>
       <c r="Z97" s="132" t="n">
-        <v>16363.1543764469</v>
+        <v>16363.15437644689</v>
       </c>
     </row>
     <row r="98">
@@ -20192,13 +20192,13 @@
         <v>976</v>
       </c>
       <c r="J98" s="130" t="n">
-        <v>351.9287478386029</v>
+        <v>351.9287478386028</v>
       </c>
       <c r="K98" s="131" t="n">
-        <v>695.26532200108</v>
+        <v>695.2653220010801</v>
       </c>
       <c r="L98" s="131" t="n">
-        <v>4.363987808065344</v>
+        <v>4.363987808065345</v>
       </c>
       <c r="M98" s="131" t="n">
         <v>0</v>
@@ -20207,10 +20207,10 @@
         <v>1051.558057647748</v>
       </c>
       <c r="P98" s="130" t="n">
-        <v>344.867797743876</v>
+        <v>344.8677977438759</v>
       </c>
       <c r="Q98" s="131" t="n">
-        <v>695.6708181072372</v>
+        <v>695.6708181072373</v>
       </c>
       <c r="R98" s="131" t="n">
         <v>4.376881306996877</v>
@@ -20222,10 +20222,10 @@
         <v>1044.91549715811</v>
       </c>
       <c r="V98" s="130" t="n">
-        <v>337.2252462051625</v>
+        <v>337.2252462051626</v>
       </c>
       <c r="W98" s="131" t="n">
-        <v>693.7423997998152</v>
+        <v>693.7423997998151</v>
       </c>
       <c r="X98" s="131" t="n">
         <v>4.349920807420687</v>
@@ -20280,10 +20280,10 @@
         <v>2604.95332839858</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>42.03577551248054</v>
+        <v>42.03577551247963</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>5099.728555144816</v>
+        <v>5099.728555144814</v>
       </c>
       <c r="T99" s="132" t="n">
         <v>10943.97587903814</v>
@@ -20298,7 +20298,7 @@
         <v>51.03255827472276</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>5541.410161234373</v>
+        <v>5541.410161234372</v>
       </c>
       <c r="Z99" s="132" t="n">
         <v>12535.77328412354</v>
@@ -20350,10 +20350,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>5099.725056957099</v>
+        <v>5099.725056957098</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>5099.725056957099</v>
+        <v>5099.725056957098</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -20567,10 +20567,10 @@
         <v>264737.8059749066</v>
       </c>
       <c r="X103" s="140" t="n">
-        <v>4142.034055145594</v>
+        <v>4142.034055145593</v>
       </c>
       <c r="Y103" s="140" t="n">
-        <v>507.7439456670622</v>
+        <v>507.7439456670623</v>
       </c>
       <c r="Z103" s="141" t="n">
         <v>545672.9854099642</v>
@@ -20619,10 +20619,10 @@
         <v>273437.7993541604</v>
       </c>
       <c r="R104" s="143" t="n">
-        <v>4247.739981535529</v>
+        <v>4247.739981535528</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>5630.618451034226</v>
+        <v>5630.618451034225</v>
       </c>
       <c r="T104" s="144" t="n">
         <v>574767.6038082013</v>
@@ -20634,13 +20634,13 @@
         <v>275824.1403448745</v>
       </c>
       <c r="X104" s="143" t="n">
-        <v>4287.484946119356</v>
+        <v>4287.484946119355</v>
       </c>
       <c r="Y104" s="143" t="n">
         <v>6050.69352997534</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>581216.5896308239</v>
+        <v>581216.5896308238</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -21635,7 +21635,7 @@
         <v>1071061</v>
       </c>
       <c r="G25" s="41" t="n">
-        <v>29.40708221676762</v>
+        <v>29.40708221676763</v>
       </c>
       <c r="H25" s="42" t="n">
         <v>24.11919292003513</v>
@@ -21673,7 +21673,7 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>9597999.977926435</v>
+        <v>9527427.014243346</v>
       </c>
       <c r="AI25" s="46" t="n">
         <v>12769.54856496323</v>
@@ -21712,7 +21712,7 @@
         <v>1314049</v>
       </c>
       <c r="G26" s="52" t="n">
-        <v>98.07134749774573</v>
+        <v>98.07134749774571</v>
       </c>
       <c r="H26" s="53" t="n">
         <v>74.05596257889991</v>
@@ -21904,7 +21904,7 @@
         </is>
       </c>
       <c r="AH28" s="122" t="n">
-        <v>467965.6858161184</v>
+        <v>467965.6858161185</v>
       </c>
       <c r="AI28" s="56" t="n">
         <v>745.1977318077995</v>
@@ -21981,7 +21981,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>250680.0442883839</v>
+        <v>250680.0442883838</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>218.3281904331627</v>
@@ -22058,7 +22058,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>234494.3510725113</v>
+        <v>234495.9382616249</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>583.4569193065761</v>
@@ -22192,7 +22192,7 @@
         </is>
       </c>
       <c r="AH32" s="122" t="n">
-        <v>161088.4542322382</v>
+        <v>158543.5269110456</v>
       </c>
       <c r="AI32" s="56" t="n">
         <v>278.4775381563741</v>
@@ -22272,7 +22272,7 @@
         <v>152313.343536535</v>
       </c>
       <c r="AI33" s="56" t="n">
-        <v>386.0779912577577</v>
+        <v>386.0779912577576</v>
       </c>
       <c r="AK33" s="123" t="n">
         <v>9</v>
@@ -22349,7 +22349,7 @@
         <v>148081.8312437994</v>
       </c>
       <c r="AI34" s="56" t="n">
-        <v>49.50464783077527</v>
+        <v>49.50464783077526</v>
       </c>
       <c r="AK34" s="123" t="n">
         <v>10</v>
@@ -22654,7 +22654,7 @@
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>100514.8986135326</v>
+        <v>100532.8754548712</v>
       </c>
       <c r="AI38" s="56" t="n">
         <v>147.4348574158096</v>
@@ -22717,7 +22717,7 @@
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>81399.42466296823</v>
+        <v>81405.75451714285</v>
       </c>
       <c r="AI39" s="56" t="n">
         <v>197.9842290078921</v>
@@ -22784,7 +22784,7 @@
         </is>
       </c>
       <c r="AH40" s="122" t="n">
-        <v>76209.36496274143</v>
+        <v>76210.48820618891</v>
       </c>
       <c r="AI40" s="56" t="n">
         <v>70.82665710335527</v>
@@ -22941,7 +22941,7 @@
         <v>66764.26703950249</v>
       </c>
       <c r="AI42" s="56" t="n">
-        <v>59.25783071991071</v>
+        <v>59.25783071991072</v>
       </c>
       <c r="AK42" s="123" t="n">
         <v>18</v>
@@ -23015,7 +23015,7 @@
         </is>
       </c>
       <c r="AH43" s="122" t="n">
-        <v>62054.60747581835</v>
+        <v>62060.39210193272</v>
       </c>
       <c r="AI43" s="56" t="n">
         <v>62.77817334161035</v>
@@ -23092,7 +23092,7 @@
         </is>
       </c>
       <c r="AH44" s="125" t="n">
-        <v>59901.00586583804</v>
+        <v>59901.00586583806</v>
       </c>
       <c r="AI44" s="84" t="n">
         <v>140.1553635753655</v>
@@ -23266,7 +23266,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>10426266.599636</v>
+        <v>10355693.63595291</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>20672.39396831167</v>
@@ -23282,10 +23282,10 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>1268825.844037802</v>
+        <v>1268827.431226915</v>
       </c>
       <c r="AH50" s="56" t="n">
-        <v>6395.928872955813</v>
+        <v>6395.928872955812</v>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1" thickBot="1">
@@ -23328,7 +23328,7 @@
         </is>
       </c>
       <c r="AG51" s="122" t="n">
-        <v>467965.6858161184</v>
+        <v>467965.6858161185</v>
       </c>
       <c r="AH51" s="56" t="n">
         <v>767.6697553968106</v>
@@ -23445,14 +23445,14 @@
       </c>
       <c r="AF52" t="inlineStr">
         <is>
-          <t>MIGRAINE PRODUCTS</t>
+          <t>DIGESTIVE ENZYMES</t>
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>400752.3214827746</v>
+        <v>398761.8755321832</v>
       </c>
       <c r="AH52" s="56" t="n">
-        <v>626.1720366637545</v>
+        <v>267.832838263938</v>
       </c>
     </row>
     <row r="53">
@@ -23526,14 +23526,14 @@
       </c>
       <c r="AF53" t="inlineStr">
         <is>
-          <t>DIGESTIVE ENZYMES</t>
+          <t>MIGRAINE PRODUCTS</t>
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>398761.8755321832</v>
+        <v>398214.3020311438</v>
       </c>
       <c r="AH53" s="56" t="n">
-        <v>267.832838263938</v>
+        <v>626.1720366637545</v>
       </c>
     </row>
     <row r="54">
@@ -23611,7 +23611,7 @@
         </is>
       </c>
       <c r="AG54" s="122" t="n">
-        <v>180608.7979594308</v>
+        <v>180624.6572362439</v>
       </c>
       <c r="AH54" s="56" t="n">
         <v>416.1816363077455</v>
@@ -23900,7 +23900,7 @@
         <v>0</v>
       </c>
       <c r="Q58" s="131" t="n">
-        <v>7.09762893823543</v>
+        <v>7.097628938235432</v>
       </c>
       <c r="R58" s="131" t="n">
         <v>0</v>
@@ -23909,7 +23909,7 @@
         <v>0</v>
       </c>
       <c r="T58" s="132" t="n">
-        <v>7.09762893823543</v>
+        <v>7.097628938235432</v>
       </c>
       <c r="V58" s="130" t="n">
         <v>0</v>
@@ -23935,7 +23935,7 @@
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>139381.0254077678</v>
+        <v>139399.0022491063</v>
       </c>
       <c r="AH58" s="56" t="n">
         <v>203.221019681251</v>
@@ -23963,7 +23963,7 @@
         <v>19</v>
       </c>
       <c r="J59" s="130" t="n">
-        <v>24.87719139716618</v>
+        <v>24.87719139716617</v>
       </c>
       <c r="K59" s="131" t="n">
         <v>0</v>
@@ -23975,7 +23975,7 @@
         <v>0.6176590635903295</v>
       </c>
       <c r="N59" s="132" t="n">
-        <v>25.49485046075651</v>
+        <v>25.4948504607565</v>
       </c>
       <c r="P59" s="130" t="n">
         <v>27.65663487526179</v>
@@ -23987,7 +23987,7 @@
         <v>0</v>
       </c>
       <c r="S59" s="131" t="n">
-        <v>0.6107794764899805</v>
+        <v>0.6107794764899804</v>
       </c>
       <c r="T59" s="132" t="n">
         <v>28.26741435175177</v>
@@ -24016,7 +24016,7 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>116137.4177379351</v>
+        <v>116146.2281672098</v>
       </c>
       <c r="AH59" s="56" t="n">
         <v>288.1655270376649</v>
@@ -24059,7 +24059,7 @@
         <v>12.15752497820848</v>
       </c>
       <c r="P60" s="130" t="n">
-        <v>6.618249046619541</v>
+        <v>6.618249046619539</v>
       </c>
       <c r="Q60" s="131" t="n">
         <v>0</v>
@@ -24071,7 +24071,7 @@
         <v>0</v>
       </c>
       <c r="T60" s="132" t="n">
-        <v>6.618249046619541</v>
+        <v>6.618249046619539</v>
       </c>
       <c r="V60" s="130" t="n">
         <v>6.034114128367583</v>
@@ -24125,13 +24125,13 @@
         <v>5271</v>
       </c>
       <c r="J61" s="130" t="n">
-        <v>6044.873869593556</v>
+        <v>6044.873869593554</v>
       </c>
       <c r="K61" s="131" t="n">
-        <v>3778.992897518413</v>
+        <v>3778.992897518414</v>
       </c>
       <c r="L61" s="131" t="n">
-        <v>69.29836851932255</v>
+        <v>69.29836851932257</v>
       </c>
       <c r="M61" s="131" t="n">
         <v>0</v>
@@ -24140,10 +24140,10 @@
         <v>9893.165135631292</v>
       </c>
       <c r="P61" s="130" t="n">
-        <v>6228.776889941023</v>
+        <v>6228.77688994102</v>
       </c>
       <c r="Q61" s="131" t="n">
-        <v>3999.114543167051</v>
+        <v>3999.114543167052</v>
       </c>
       <c r="R61" s="131" t="n">
         <v>73.5852791072068</v>
@@ -24155,7 +24155,7 @@
         <v>10301.47671221528</v>
       </c>
       <c r="V61" s="130" t="n">
-        <v>6447.101264258591</v>
+        <v>6447.101264258589</v>
       </c>
       <c r="W61" s="131" t="n">
         <v>4230.066745339464</v>
@@ -24206,13 +24206,13 @@
         <v>976</v>
       </c>
       <c r="J62" s="130" t="n">
-        <v>351.9287478386029</v>
+        <v>351.9287478386028</v>
       </c>
       <c r="K62" s="131" t="n">
-        <v>695.26532200108</v>
+        <v>695.2653220010801</v>
       </c>
       <c r="L62" s="131" t="n">
-        <v>4.363987808065344</v>
+        <v>4.363987808065345</v>
       </c>
       <c r="M62" s="131" t="n">
         <v>0</v>
@@ -24221,10 +24221,10 @@
         <v>1051.558057647748</v>
       </c>
       <c r="P62" s="130" t="n">
-        <v>344.867797743876</v>
+        <v>344.8677977438759</v>
       </c>
       <c r="Q62" s="131" t="n">
-        <v>695.6708181072372</v>
+        <v>695.6708181072373</v>
       </c>
       <c r="R62" s="131" t="n">
         <v>4.376881306996877</v>
@@ -24236,10 +24236,10 @@
         <v>1044.91549715811</v>
       </c>
       <c r="V62" s="130" t="n">
-        <v>337.2252462051625</v>
+        <v>337.2252462051626</v>
       </c>
       <c r="W62" s="131" t="n">
-        <v>693.7423997998152</v>
+        <v>693.7423997998151</v>
       </c>
       <c r="X62" s="131" t="n">
         <v>4.349920807420687</v>
@@ -24293,7 +24293,7 @@
         <v>2139.409809914607</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>34.42048685206294</v>
+        <v>34.42048685206299</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>4055.662939861252</v>
@@ -24308,10 +24308,10 @@
         <v>2604.953328398544</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>42.03577551248003</v>
+        <v>42.03577551248006</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>4367.592784770584</v>
+        <v>4367.592784770583</v>
       </c>
       <c r="T63" s="132" t="n">
         <v>10176.20914193729</v>
@@ -24320,7 +24320,7 @@
         <v>3718.42453944005</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>3171.189177178967</v>
+        <v>3171.189177178965</v>
       </c>
       <c r="X63" s="131" t="n">
         <v>51.03255827472316</v>
@@ -24377,10 +24377,10 @@
         <v>0</v>
       </c>
       <c r="M64" s="134" t="n">
-        <v>4055.659530255102</v>
+        <v>4055.659530255103</v>
       </c>
       <c r="N64" s="135" t="n">
-        <v>4055.659530255102</v>
+        <v>4055.659530255103</v>
       </c>
       <c r="P64" s="133" t="n">
         <v>0</v>
@@ -24392,10 +24392,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>4367.589286582867</v>
+        <v>4367.589286582866</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>4367.589286582867</v>
+        <v>4367.589286582866</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -24507,7 +24507,7 @@
         </is>
       </c>
       <c r="AG65" s="122" t="n">
-        <v>35380.24338444944</v>
+        <v>35382.45525520734</v>
       </c>
       <c r="AH65" s="56" t="n">
         <v>57.89489579250349</v>
@@ -24632,10 +24632,10 @@
         <v>48404.11294602313</v>
       </c>
       <c r="P67" s="139" t="n">
-        <v>29468.774697933</v>
+        <v>29468.77469793299</v>
       </c>
       <c r="Q67" s="140" t="n">
-        <v>10340.41686575611</v>
+        <v>10340.41686575612</v>
       </c>
       <c r="R67" s="140" t="n">
         <v>142.2558187419964</v>
@@ -24644,19 +24644,19 @@
         <v>529.4434178862319</v>
       </c>
       <c r="T67" s="141" t="n">
-        <v>40480.89080031734</v>
+        <v>40480.89080031733</v>
       </c>
       <c r="V67" s="139" t="n">
         <v>27700.89671012675</v>
       </c>
       <c r="W67" s="140" t="n">
-        <v>8009.429015133594</v>
+        <v>8009.429015133596</v>
       </c>
       <c r="X67" s="140" t="n">
         <v>115.5740789429929</v>
       </c>
       <c r="Y67" s="140" t="n">
-        <v>507.7439456670622</v>
+        <v>507.7439456670623</v>
       </c>
       <c r="Z67" s="141" t="n">
         <v>36333.6437498704</v>
@@ -24698,7 +24698,7 @@
         <v>15292</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>41792.11030289561</v>
+        <v>41792.1103028956</v>
       </c>
       <c r="K68" s="143" t="n">
         <v>21604.37829025543</v>
@@ -24716,16 +24716,16 @@
         <v>39238.32152279546</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>17647.25318436718</v>
+        <v>17647.25318436719</v>
       </c>
       <c r="R68" s="143" t="n">
         <v>262.2537546686801</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>4897.646982133306</v>
+        <v>4897.646982133305</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>66413.0647305475</v>
+        <v>66413.06473054748</v>
       </c>
       <c r="V68" s="142" t="n">
         <v>38240.73362856136</v>
@@ -25334,10 +25334,10 @@
         <v>0</v>
       </c>
       <c r="S77" s="131" t="n">
-        <v>0.8356985266883201</v>
+        <v>0.8356985266883199</v>
       </c>
       <c r="T77" s="132" t="n">
-        <v>0.8356985266883201</v>
+        <v>0.8356985266883199</v>
       </c>
       <c r="V77" s="130" t="n">
         <v>0</v>
@@ -25349,10 +25349,10 @@
         <v>0</v>
       </c>
       <c r="Y77" s="131" t="n">
-        <v>0.8963748172115764</v>
+        <v>0.896374817211576</v>
       </c>
       <c r="Z77" s="132" t="n">
-        <v>0.8963748172115764</v>
+        <v>0.896374817211576</v>
       </c>
     </row>
     <row r="78">
@@ -25407,7 +25407,7 @@
         <v>19.96087013213621</v>
       </c>
       <c r="V78" s="130" t="n">
-        <v>22.02775740512094</v>
+        <v>22.02775740512093</v>
       </c>
       <c r="W78" s="131" t="n">
         <v>0</v>
@@ -25419,7 +25419,7 @@
         <v>0</v>
       </c>
       <c r="Z78" s="132" t="n">
-        <v>22.02775740512094</v>
+        <v>22.02775740512093</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1">
@@ -25462,7 +25462,7 @@
         <v>2558.682056625253</v>
       </c>
       <c r="Q79" s="131" t="n">
-        <v>2925.262718709261</v>
+        <v>2925.26271870926</v>
       </c>
       <c r="R79" s="131" t="n">
         <v>12.15252135439121</v>
@@ -25474,10 +25474,10 @@
         <v>5496.097296688905</v>
       </c>
       <c r="V79" s="130" t="n">
-        <v>2611.881295037886</v>
+        <v>2611.881295037884</v>
       </c>
       <c r="W79" s="131" t="n">
-        <v>2984.036659919333</v>
+        <v>2984.036659919334</v>
       </c>
       <c r="X79" s="131" t="n">
         <v>12.40600426369416</v>
@@ -25486,7 +25486,7 @@
         <v>0</v>
       </c>
       <c r="Z79" s="132" t="n">
-        <v>5608.323959220913</v>
+        <v>5608.323959220912</v>
       </c>
     </row>
     <row r="80">
@@ -25602,10 +25602,10 @@
         <v>0</v>
       </c>
       <c r="S81" s="131" t="n">
-        <v>732.1357703742319</v>
+        <v>732.1357703742317</v>
       </c>
       <c r="T81" s="132" t="n">
-        <v>767.7667371008351</v>
+        <v>767.7667371008349</v>
       </c>
       <c r="V81" s="130" t="n">
         <v>53.71684799538343</v>
@@ -25617,10 +25617,10 @@
         <v>0</v>
       </c>
       <c r="Y81" s="131" t="n">
-        <v>880.0595490867238</v>
+        <v>880.0595490867235</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>933.7763970821072</v>
+        <v>933.7763970821069</v>
       </c>
     </row>
     <row r="82">
@@ -25669,10 +25669,10 @@
         <v>0</v>
       </c>
       <c r="S82" s="134" t="n">
-        <v>732.1357703742319</v>
+        <v>732.1357703742317</v>
       </c>
       <c r="T82" s="135" t="n">
-        <v>732.1357703742319</v>
+        <v>732.1357703742317</v>
       </c>
       <c r="V82" s="133" t="n">
         <v>0</v>
@@ -25684,10 +25684,10 @@
         <v>0</v>
       </c>
       <c r="Y82" s="134" t="n">
-        <v>880.0595490867238</v>
+        <v>880.0595490867235</v>
       </c>
       <c r="Z82" s="135" t="n">
-        <v>880.0595490867238</v>
+        <v>880.0595490867235</v>
       </c>
     </row>
     <row r="83">
@@ -25871,7 +25871,7 @@
         <v>252865.283451084</v>
       </c>
       <c r="R85" s="140" t="n">
-        <v>3973.333705512458</v>
+        <v>3973.333705512457</v>
       </c>
       <c r="S85" s="140" t="n">
         <v>0</v>
@@ -25886,7 +25886,7 @@
         <v>256728.376959773</v>
       </c>
       <c r="X85" s="140" t="n">
-        <v>4026.459976202601</v>
+        <v>4026.4599762026</v>
       </c>
       <c r="Y85" s="140" t="n">
         <v>0</v>
@@ -25938,10 +25938,10 @@
         <v>255790.5461697932</v>
       </c>
       <c r="R86" s="143" t="n">
-        <v>3985.486226866849</v>
+        <v>3985.486226866848</v>
       </c>
       <c r="S86" s="143" t="n">
-        <v>732.9714689009203</v>
+        <v>732.9714689009201</v>
       </c>
       <c r="T86" s="144" t="n">
         <v>508354.5390776537</v>
@@ -25953,13 +25953,13 @@
         <v>259712.4136196924</v>
       </c>
       <c r="X86" s="143" t="n">
-        <v>4038.865980466295</v>
+        <v>4038.865980466294</v>
       </c>
       <c r="Y86" s="143" t="n">
-        <v>880.9559239039354</v>
+        <v>880.9559239039351</v>
       </c>
       <c r="Z86" s="144" t="n">
-        <v>516784.425697706</v>
+        <v>516784.4256977059</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" thickBot="1">
@@ -26466,7 +26466,7 @@
         <v>0</v>
       </c>
       <c r="Q94" s="131" t="n">
-        <v>7.09762893823543</v>
+        <v>7.097628938235432</v>
       </c>
       <c r="R94" s="131" t="n">
         <v>0</v>
@@ -26475,7 +26475,7 @@
         <v>0</v>
       </c>
       <c r="T94" s="132" t="n">
-        <v>7.09762893823543</v>
+        <v>7.097628938235432</v>
       </c>
       <c r="V94" s="130" t="n">
         <v>0</v>
@@ -26515,7 +26515,7 @@
         <v>19</v>
       </c>
       <c r="J95" s="130" t="n">
-        <v>24.87719139716618</v>
+        <v>24.87719139716617</v>
       </c>
       <c r="K95" s="131" t="n">
         <v>0</v>
@@ -26527,7 +26527,7 @@
         <v>1.367136085871659</v>
       </c>
       <c r="N95" s="132" t="n">
-        <v>26.24432748303784</v>
+        <v>26.24432748303783</v>
       </c>
       <c r="P95" s="130" t="n">
         <v>27.65663487526179</v>
@@ -26539,7 +26539,7 @@
         <v>0</v>
       </c>
       <c r="S95" s="131" t="n">
-        <v>1.446478003178301</v>
+        <v>1.4464780031783</v>
       </c>
       <c r="T95" s="132" t="n">
         <v>29.10311287844009</v>
@@ -26554,7 +26554,7 @@
         <v>0</v>
       </c>
       <c r="Y95" s="131" t="n">
-        <v>1.539423073904819</v>
+        <v>1.539423073904818</v>
       </c>
       <c r="Z95" s="132" t="n">
         <v>32.59117747634145</v>
@@ -26612,7 +26612,7 @@
         <v>26.57911917875575</v>
       </c>
       <c r="V96" s="130" t="n">
-        <v>28.06187153348852</v>
+        <v>28.06187153348851</v>
       </c>
       <c r="W96" s="131" t="n">
         <v>0</v>
@@ -26624,7 +26624,7 @@
         <v>0</v>
       </c>
       <c r="Z96" s="132" t="n">
-        <v>28.06187153348852</v>
+        <v>28.06187153348851</v>
       </c>
     </row>
     <row r="97">
@@ -26649,10 +26649,10 @@
         <v>9704</v>
       </c>
       <c r="J97" s="130" t="n">
-        <v>8521.815565172985</v>
+        <v>8521.815565172983</v>
       </c>
       <c r="K97" s="131" t="n">
-        <v>6628.085294105205</v>
+        <v>6628.085294105206</v>
       </c>
       <c r="L97" s="131" t="n">
         <v>81.12125915531615</v>
@@ -26664,10 +26664,10 @@
         <v>15231.02211843351</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>8787.458946566276</v>
+        <v>8787.458946566274</v>
       </c>
       <c r="Q97" s="131" t="n">
-        <v>6924.377261876311</v>
+        <v>6924.377261876312</v>
       </c>
       <c r="R97" s="131" t="n">
         <v>85.73780046159801</v>
@@ -26679,7 +26679,7 @@
         <v>15797.57400890418</v>
       </c>
       <c r="V97" s="130" t="n">
-        <v>9058.982559296477</v>
+        <v>9058.982559296473</v>
       </c>
       <c r="W97" s="131" t="n">
         <v>7214.103405258798</v>
@@ -26691,7 +26691,7 @@
         <v>0</v>
       </c>
       <c r="Z97" s="132" t="n">
-        <v>16363.1543764469</v>
+        <v>16363.15437644689</v>
       </c>
     </row>
     <row r="98">
@@ -26716,13 +26716,13 @@
         <v>976</v>
       </c>
       <c r="J98" s="130" t="n">
-        <v>351.9287478386029</v>
+        <v>351.9287478386028</v>
       </c>
       <c r="K98" s="131" t="n">
-        <v>695.26532200108</v>
+        <v>695.2653220010801</v>
       </c>
       <c r="L98" s="131" t="n">
-        <v>4.363987808065344</v>
+        <v>4.363987808065345</v>
       </c>
       <c r="M98" s="131" t="n">
         <v>0</v>
@@ -26731,10 +26731,10 @@
         <v>1051.558057647748</v>
       </c>
       <c r="P98" s="130" t="n">
-        <v>344.867797743876</v>
+        <v>344.8677977438759</v>
       </c>
       <c r="Q98" s="131" t="n">
-        <v>695.6708181072372</v>
+        <v>695.6708181072373</v>
       </c>
       <c r="R98" s="131" t="n">
         <v>4.376881306996877</v>
@@ -26746,10 +26746,10 @@
         <v>1044.91549715811</v>
       </c>
       <c r="V98" s="130" t="n">
-        <v>337.2252462051625</v>
+        <v>337.2252462051626</v>
       </c>
       <c r="W98" s="131" t="n">
-        <v>693.7423997998152</v>
+        <v>693.7423997998151</v>
       </c>
       <c r="X98" s="131" t="n">
         <v>4.349920807420687</v>
@@ -26804,10 +26804,10 @@
         <v>2604.95332839858</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>42.03577551248054</v>
+        <v>42.03577551247963</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>5099.728555144816</v>
+        <v>5099.728555144814</v>
       </c>
       <c r="T99" s="132" t="n">
         <v>10943.97587903814</v>
@@ -26822,7 +26822,7 @@
         <v>51.03255827472276</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>5541.410161234373</v>
+        <v>5541.410161234372</v>
       </c>
       <c r="Z99" s="132" t="n">
         <v>12535.77328412354</v>
@@ -26874,10 +26874,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>5099.725056957099</v>
+        <v>5099.725056957098</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>5099.725056957099</v>
+        <v>5099.725056957098</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -27091,10 +27091,10 @@
         <v>264737.8059749066</v>
       </c>
       <c r="X103" s="140" t="n">
-        <v>4142.034055145594</v>
+        <v>4142.034055145593</v>
       </c>
       <c r="Y103" s="140" t="n">
-        <v>507.7439456670622</v>
+        <v>507.7439456670623</v>
       </c>
       <c r="Z103" s="141" t="n">
         <v>545672.9854099642</v>
@@ -27143,10 +27143,10 @@
         <v>273437.7993541604</v>
       </c>
       <c r="R104" s="143" t="n">
-        <v>4247.739981535529</v>
+        <v>4247.739981535528</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>5630.618451034226</v>
+        <v>5630.618451034225</v>
       </c>
       <c r="T104" s="144" t="n">
         <v>574767.6038082013</v>
@@ -27158,13 +27158,13 @@
         <v>275824.1403448745</v>
       </c>
       <c r="X104" s="143" t="n">
-        <v>4287.484946119356</v>
+        <v>4287.484946119355</v>
       </c>
       <c r="Y104" s="143" t="n">
         <v>6050.69352997534</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>581216.5896308239</v>
+        <v>581216.5896308238</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
@@ -28159,7 +28159,7 @@
         <v>1071061</v>
       </c>
       <c r="G25" s="41" t="n">
-        <v>29.40708221676762</v>
+        <v>29.40708221676763</v>
       </c>
       <c r="H25" s="42" t="n">
         <v>24.11919292003513</v>
@@ -28197,7 +28197,7 @@
         </is>
       </c>
       <c r="AH25" s="119" t="n">
-        <v>11954844.10030086</v>
+        <v>11834823.69873812</v>
       </c>
       <c r="AI25" s="46" t="n">
         <v>15323.44213046236</v>
@@ -28236,7 +28236,7 @@
         <v>1314049</v>
       </c>
       <c r="G26" s="52" t="n">
-        <v>98.07134749774573</v>
+        <v>98.07134749774571</v>
       </c>
       <c r="H26" s="53" t="n">
         <v>74.05596257889991</v>
@@ -28274,7 +28274,7 @@
         </is>
       </c>
       <c r="AH26" s="122" t="n">
-        <v>951956.7819181825</v>
+        <v>951956.7819181824</v>
       </c>
       <c r="AI26" s="56" t="n">
         <v>1266.912187031183</v>
@@ -28505,7 +28505,7 @@
         </is>
       </c>
       <c r="AH29" s="122" t="n">
-        <v>272901.3316407847</v>
+        <v>272901.3316407848</v>
       </c>
       <c r="AI29" s="56" t="n">
         <v>224.4086305367263</v>
@@ -28582,7 +28582,7 @@
         </is>
       </c>
       <c r="AH30" s="122" t="n">
-        <v>184743.5989916826</v>
+        <v>182595.928620907</v>
       </c>
       <c r="AI30" s="56" t="n">
         <v>299.1015846322352</v>
@@ -28796,7 +28796,7 @@
         <v>132144.4016893462</v>
       </c>
       <c r="AI33" s="56" t="n">
-        <v>423.4029250633002</v>
+        <v>423.4029250633001</v>
       </c>
       <c r="AK33" s="123" t="n">
         <v>9</v>
@@ -28870,7 +28870,7 @@
         </is>
       </c>
       <c r="AH34" s="122" t="n">
-        <v>121104.1180196385</v>
+        <v>121130.6189115226</v>
       </c>
       <c r="AI34" s="56" t="n">
         <v>165.4086408833709</v>
@@ -28950,7 +28950,7 @@
         <v>113833.5430222364</v>
       </c>
       <c r="AI35" s="56" t="n">
-        <v>228.2162379852892</v>
+        <v>228.2162379852893</v>
       </c>
       <c r="AK35" s="123" t="n">
         <v>11</v>
@@ -29024,7 +29024,7 @@
         </is>
       </c>
       <c r="AH36" s="122" t="n">
-        <v>87232.73638597781</v>
+        <v>87234.24160123405</v>
       </c>
       <c r="AI36" s="56" t="n">
         <v>76.07207932842975</v>
@@ -29101,7 +29101,7 @@
         </is>
       </c>
       <c r="AH37" s="122" t="n">
-        <v>86239.4363499087</v>
+        <v>86247.72213164018</v>
       </c>
       <c r="AI37" s="56" t="n">
         <v>196.0281448252941</v>
@@ -29178,7 +29178,7 @@
         </is>
       </c>
       <c r="AH38" s="122" t="n">
-        <v>72238.99042074622</v>
+        <v>72239.41645283032</v>
       </c>
       <c r="AI38" s="56" t="n">
         <v>247.7889289672761</v>
@@ -29241,7 +29241,7 @@
         </is>
       </c>
       <c r="AH39" s="122" t="n">
-        <v>71891.09086100262</v>
+        <v>71899.51337620852</v>
       </c>
       <c r="AI39" s="56" t="n">
         <v>67.42752485929</v>
@@ -29385,10 +29385,10 @@
         </is>
       </c>
       <c r="AH41" s="122" t="n">
-        <v>66969.54519543488</v>
+        <v>66969.5451954349</v>
       </c>
       <c r="AI41" s="56" t="n">
-        <v>56.49108260359809</v>
+        <v>56.49108260359808</v>
       </c>
       <c r="AK41" s="123" t="n">
         <v>17</v>
@@ -29790,7 +29790,7 @@
         </is>
       </c>
       <c r="AG49" s="119" t="n">
-        <v>12906800.88221904</v>
+        <v>12786780.4806563</v>
       </c>
       <c r="AH49" s="46" t="n">
         <v>24095.60052817913</v>
@@ -29806,7 +29806,7 @@
         </is>
       </c>
       <c r="AG50" s="122" t="n">
-        <v>1007460.798103358</v>
+        <v>1007461.224135442</v>
       </c>
       <c r="AH50" s="56" t="n">
         <v>4257.422574251343</v>
@@ -29973,7 +29973,7 @@
         </is>
       </c>
       <c r="AG52" s="122" t="n">
-        <v>457700.9692608994</v>
+        <v>455563.226620586</v>
       </c>
       <c r="AH52" s="56" t="n">
         <v>672.5463376990722</v>
@@ -30054,7 +30054,7 @@
         </is>
       </c>
       <c r="AG53" s="122" t="n">
-        <v>432787.8299096154</v>
+        <v>432787.8299096155</v>
       </c>
       <c r="AH53" s="56" t="n">
         <v>275.2919828095887</v>
@@ -30378,7 +30378,7 @@
         </is>
       </c>
       <c r="AG57" s="122" t="n">
-        <v>123014.8857602777</v>
+        <v>123026.4278810774</v>
       </c>
       <c r="AH57" s="56" t="n">
         <v>285.3184516305328</v>
@@ -30424,7 +30424,7 @@
         <v>0</v>
       </c>
       <c r="Q58" s="131" t="n">
-        <v>7.09762893823543</v>
+        <v>7.097628938235432</v>
       </c>
       <c r="R58" s="131" t="n">
         <v>0</v>
@@ -30433,7 +30433,7 @@
         <v>0</v>
       </c>
       <c r="T58" s="132" t="n">
-        <v>7.09762893823543</v>
+        <v>7.097628938235432</v>
       </c>
       <c r="V58" s="130" t="n">
         <v>0</v>
@@ -30459,7 +30459,7 @@
         </is>
       </c>
       <c r="AG58" s="122" t="n">
-        <v>121104.1180196385</v>
+        <v>121130.6189115226</v>
       </c>
       <c r="AH58" s="56" t="n">
         <v>178.5021877230272</v>
@@ -30487,7 +30487,7 @@
         <v>19</v>
       </c>
       <c r="J59" s="130" t="n">
-        <v>24.87719139716618</v>
+        <v>24.87719139716617</v>
       </c>
       <c r="K59" s="131" t="n">
         <v>0</v>
@@ -30499,7 +30499,7 @@
         <v>0.6176590635903295</v>
       </c>
       <c r="N59" s="132" t="n">
-        <v>25.49485046075651</v>
+        <v>25.4948504607565</v>
       </c>
       <c r="P59" s="130" t="n">
         <v>27.65663487526179</v>
@@ -30511,7 +30511,7 @@
         <v>0</v>
       </c>
       <c r="S59" s="131" t="n">
-        <v>0.6107794764899805</v>
+        <v>0.6107794764899804</v>
       </c>
       <c r="T59" s="132" t="n">
         <v>28.26741435175177</v>
@@ -30540,7 +30540,7 @@
         </is>
       </c>
       <c r="AG59" s="122" t="n">
-        <v>79997.1622449626</v>
+        <v>80018.33548781663</v>
       </c>
       <c r="AH59" s="56" t="n">
         <v>195.1197448750256</v>
@@ -30583,7 +30583,7 @@
         <v>12.15752497820848</v>
       </c>
       <c r="P60" s="130" t="n">
-        <v>6.618249046619541</v>
+        <v>6.618249046619539</v>
       </c>
       <c r="Q60" s="131" t="n">
         <v>0</v>
@@ -30595,7 +30595,7 @@
         <v>0</v>
       </c>
       <c r="T60" s="132" t="n">
-        <v>6.618249046619541</v>
+        <v>6.618249046619539</v>
       </c>
       <c r="V60" s="130" t="n">
         <v>6.034114128367583</v>
@@ -30649,13 +30649,13 @@
         <v>5271</v>
       </c>
       <c r="J61" s="130" t="n">
-        <v>6044.873869593556</v>
+        <v>6044.873869593554</v>
       </c>
       <c r="K61" s="131" t="n">
-        <v>3778.992897518413</v>
+        <v>3778.992897518414</v>
       </c>
       <c r="L61" s="131" t="n">
-        <v>69.29836851932255</v>
+        <v>69.29836851932257</v>
       </c>
       <c r="M61" s="131" t="n">
         <v>0</v>
@@ -30664,10 +30664,10 @@
         <v>9893.165135631292</v>
       </c>
       <c r="P61" s="130" t="n">
-        <v>6228.776889941023</v>
+        <v>6228.77688994102</v>
       </c>
       <c r="Q61" s="131" t="n">
-        <v>3999.114543167051</v>
+        <v>3999.114543167052</v>
       </c>
       <c r="R61" s="131" t="n">
         <v>73.5852791072068</v>
@@ -30679,7 +30679,7 @@
         <v>10301.47671221528</v>
       </c>
       <c r="V61" s="130" t="n">
-        <v>6447.101264258591</v>
+        <v>6447.101264258589</v>
       </c>
       <c r="W61" s="131" t="n">
         <v>4230.066745339464</v>
@@ -30730,13 +30730,13 @@
         <v>976</v>
       </c>
       <c r="J62" s="130" t="n">
-        <v>351.9287478386029</v>
+        <v>351.9287478386028</v>
       </c>
       <c r="K62" s="131" t="n">
-        <v>695.26532200108</v>
+        <v>695.2653220010801</v>
       </c>
       <c r="L62" s="131" t="n">
-        <v>4.363987808065344</v>
+        <v>4.363987808065345</v>
       </c>
       <c r="M62" s="131" t="n">
         <v>0</v>
@@ -30745,10 +30745,10 @@
         <v>1051.558057647748</v>
       </c>
       <c r="P62" s="130" t="n">
-        <v>344.867797743876</v>
+        <v>344.8677977438759</v>
       </c>
       <c r="Q62" s="131" t="n">
-        <v>695.6708181072372</v>
+        <v>695.6708181072373</v>
       </c>
       <c r="R62" s="131" t="n">
         <v>4.376881306996877</v>
@@ -30760,10 +30760,10 @@
         <v>1044.91549715811</v>
       </c>
       <c r="V62" s="130" t="n">
-        <v>337.2252462051625</v>
+        <v>337.2252462051626</v>
       </c>
       <c r="W62" s="131" t="n">
-        <v>693.7423997998152</v>
+        <v>693.7423997998151</v>
       </c>
       <c r="X62" s="131" t="n">
         <v>4.349920807420687</v>
@@ -30817,7 +30817,7 @@
         <v>2139.409809914607</v>
       </c>
       <c r="L63" s="131" t="n">
-        <v>34.42048685206294</v>
+        <v>34.42048685206299</v>
       </c>
       <c r="M63" s="131" t="n">
         <v>4055.662939861252</v>
@@ -30832,10 +30832,10 @@
         <v>2604.953328398544</v>
       </c>
       <c r="R63" s="131" t="n">
-        <v>42.03577551248003</v>
+        <v>42.03577551248006</v>
       </c>
       <c r="S63" s="131" t="n">
-        <v>4367.592784770584</v>
+        <v>4367.592784770583</v>
       </c>
       <c r="T63" s="132" t="n">
         <v>10176.20914193729</v>
@@ -30844,7 +30844,7 @@
         <v>3718.42453944005</v>
       </c>
       <c r="W63" s="131" t="n">
-        <v>3171.189177178967</v>
+        <v>3171.189177178965</v>
       </c>
       <c r="X63" s="131" t="n">
         <v>51.03255827472316</v>
@@ -30901,10 +30901,10 @@
         <v>0</v>
       </c>
       <c r="M64" s="134" t="n">
-        <v>4055.659530255102</v>
+        <v>4055.659530255103</v>
       </c>
       <c r="N64" s="135" t="n">
-        <v>4055.659530255102</v>
+        <v>4055.659530255103</v>
       </c>
       <c r="P64" s="133" t="n">
         <v>0</v>
@@ -30916,10 +30916,10 @@
         <v>0</v>
       </c>
       <c r="S64" s="134" t="n">
-        <v>4367.589286582867</v>
+        <v>4367.589286582866</v>
       </c>
       <c r="T64" s="135" t="n">
-        <v>4367.589286582867</v>
+        <v>4367.589286582866</v>
       </c>
       <c r="V64" s="133" t="n">
         <v>0</v>
@@ -31156,10 +31156,10 @@
         <v>48404.11294602313</v>
       </c>
       <c r="P67" s="139" t="n">
-        <v>29468.774697933</v>
+        <v>29468.77469793299</v>
       </c>
       <c r="Q67" s="140" t="n">
-        <v>10340.41686575611</v>
+        <v>10340.41686575612</v>
       </c>
       <c r="R67" s="140" t="n">
         <v>142.2558187419964</v>
@@ -31168,19 +31168,19 @@
         <v>529.4434178862319</v>
       </c>
       <c r="T67" s="141" t="n">
-        <v>40480.89080031734</v>
+        <v>40480.89080031733</v>
       </c>
       <c r="V67" s="139" t="n">
         <v>27700.89671012675</v>
       </c>
       <c r="W67" s="140" t="n">
-        <v>8009.429015133594</v>
+        <v>8009.429015133596</v>
       </c>
       <c r="X67" s="140" t="n">
         <v>115.5740789429929</v>
       </c>
       <c r="Y67" s="140" t="n">
-        <v>507.7439456670622</v>
+        <v>507.7439456670623</v>
       </c>
       <c r="Z67" s="141" t="n">
         <v>36333.6437498704</v>
@@ -31222,7 +31222,7 @@
         <v>15292</v>
       </c>
       <c r="J68" s="142" t="n">
-        <v>41792.11030289561</v>
+        <v>41792.1103028956</v>
       </c>
       <c r="K68" s="143" t="n">
         <v>21604.37829025543</v>
@@ -31240,16 +31240,16 @@
         <v>39238.32152279546</v>
       </c>
       <c r="Q68" s="143" t="n">
-        <v>17647.25318436718</v>
+        <v>17647.25318436719</v>
       </c>
       <c r="R68" s="143" t="n">
         <v>262.2537546686801</v>
       </c>
       <c r="S68" s="143" t="n">
-        <v>4897.646982133306</v>
+        <v>4897.646982133305</v>
       </c>
       <c r="T68" s="144" t="n">
-        <v>66413.0647305475</v>
+        <v>66413.06473054748</v>
       </c>
       <c r="V68" s="142" t="n">
         <v>38240.73362856136</v>
@@ -31858,10 +31858,10 @@
         <v>0</v>
       </c>
       <c r="S77" s="131" t="n">
-        <v>0.8356985266883201</v>
+        <v>0.8356985266883199</v>
       </c>
       <c r="T77" s="132" t="n">
-        <v>0.8356985266883201</v>
+        <v>0.8356985266883199</v>
       </c>
       <c r="V77" s="130" t="n">
         <v>0</v>
@@ -31873,10 +31873,10 @@
         <v>0</v>
       </c>
       <c r="Y77" s="131" t="n">
-        <v>0.8963748172115764</v>
+        <v>0.896374817211576</v>
       </c>
       <c r="Z77" s="132" t="n">
-        <v>0.8963748172115764</v>
+        <v>0.896374817211576</v>
       </c>
     </row>
     <row r="78">
@@ -31931,7 +31931,7 @@
         <v>19.96087013213621</v>
       </c>
       <c r="V78" s="130" t="n">
-        <v>22.02775740512094</v>
+        <v>22.02775740512093</v>
       </c>
       <c r="W78" s="131" t="n">
         <v>0</v>
@@ -31943,7 +31943,7 @@
         <v>0</v>
       </c>
       <c r="Z78" s="132" t="n">
-        <v>22.02775740512094</v>
+        <v>22.02775740512093</v>
       </c>
     </row>
     <row r="79" ht="15" customHeight="1">
@@ -31986,7 +31986,7 @@
         <v>2558.682056625253</v>
       </c>
       <c r="Q79" s="131" t="n">
-        <v>2925.262718709261</v>
+        <v>2925.26271870926</v>
       </c>
       <c r="R79" s="131" t="n">
         <v>12.15252135439121</v>
@@ -31998,10 +31998,10 @@
         <v>5496.097296688905</v>
       </c>
       <c r="V79" s="130" t="n">
-        <v>2611.881295037886</v>
+        <v>2611.881295037884</v>
       </c>
       <c r="W79" s="131" t="n">
-        <v>2984.036659919333</v>
+        <v>2984.036659919334</v>
       </c>
       <c r="X79" s="131" t="n">
         <v>12.40600426369416</v>
@@ -32010,7 +32010,7 @@
         <v>0</v>
       </c>
       <c r="Z79" s="132" t="n">
-        <v>5608.323959220913</v>
+        <v>5608.323959220912</v>
       </c>
     </row>
     <row r="80">
@@ -32126,10 +32126,10 @@
         <v>0</v>
       </c>
       <c r="S81" s="131" t="n">
-        <v>732.1357703742319</v>
+        <v>732.1357703742317</v>
       </c>
       <c r="T81" s="132" t="n">
-        <v>767.7667371008351</v>
+        <v>767.7667371008349</v>
       </c>
       <c r="V81" s="130" t="n">
         <v>53.71684799538343</v>
@@ -32141,10 +32141,10 @@
         <v>0</v>
       </c>
       <c r="Y81" s="131" t="n">
-        <v>880.0595490867238</v>
+        <v>880.0595490867235</v>
       </c>
       <c r="Z81" s="132" t="n">
-        <v>933.7763970821072</v>
+        <v>933.7763970821069</v>
       </c>
     </row>
     <row r="82">
@@ -32193,10 +32193,10 @@
         <v>0</v>
       </c>
       <c r="S82" s="134" t="n">
-        <v>732.1357703742319</v>
+        <v>732.1357703742317</v>
       </c>
       <c r="T82" s="135" t="n">
-        <v>732.1357703742319</v>
+        <v>732.1357703742317</v>
       </c>
       <c r="V82" s="133" t="n">
         <v>0</v>
@@ -32208,10 +32208,10 @@
         <v>0</v>
       </c>
       <c r="Y82" s="134" t="n">
-        <v>880.0595490867238</v>
+        <v>880.0595490867235</v>
       </c>
       <c r="Z82" s="135" t="n">
-        <v>880.0595490867238</v>
+        <v>880.0595490867235</v>
       </c>
     </row>
     <row r="83">
@@ -32395,7 +32395,7 @@
         <v>252865.283451084</v>
       </c>
       <c r="R85" s="140" t="n">
-        <v>3973.333705512458</v>
+        <v>3973.333705512457</v>
       </c>
       <c r="S85" s="140" t="n">
         <v>0</v>
@@ -32410,7 +32410,7 @@
         <v>256728.376959773</v>
       </c>
       <c r="X85" s="140" t="n">
-        <v>4026.459976202601</v>
+        <v>4026.4599762026</v>
       </c>
       <c r="Y85" s="140" t="n">
         <v>0</v>
@@ -32462,10 +32462,10 @@
         <v>255790.5461697932</v>
       </c>
       <c r="R86" s="143" t="n">
-        <v>3985.486226866849</v>
+        <v>3985.486226866848</v>
       </c>
       <c r="S86" s="143" t="n">
-        <v>732.9714689009203</v>
+        <v>732.9714689009201</v>
       </c>
       <c r="T86" s="144" t="n">
         <v>508354.5390776537</v>
@@ -32477,13 +32477,13 @@
         <v>259712.4136196924</v>
       </c>
       <c r="X86" s="143" t="n">
-        <v>4038.865980466295</v>
+        <v>4038.865980466294</v>
       </c>
       <c r="Y86" s="143" t="n">
-        <v>880.9559239039354</v>
+        <v>880.9559239039351</v>
       </c>
       <c r="Z86" s="144" t="n">
-        <v>516784.425697706</v>
+        <v>516784.4256977059</v>
       </c>
     </row>
     <row r="87" ht="15" customHeight="1" thickBot="1">
@@ -32990,7 +32990,7 @@
         <v>0</v>
       </c>
       <c r="Q94" s="131" t="n">
-        <v>7.09762893823543</v>
+        <v>7.097628938235432</v>
       </c>
       <c r="R94" s="131" t="n">
         <v>0</v>
@@ -32999,7 +32999,7 @@
         <v>0</v>
       </c>
       <c r="T94" s="132" t="n">
-        <v>7.09762893823543</v>
+        <v>7.097628938235432</v>
       </c>
       <c r="V94" s="130" t="n">
         <v>0</v>
@@ -33039,7 +33039,7 @@
         <v>19</v>
       </c>
       <c r="J95" s="130" t="n">
-        <v>24.87719139716618</v>
+        <v>24.87719139716617</v>
       </c>
       <c r="K95" s="131" t="n">
         <v>0</v>
@@ -33051,7 +33051,7 @@
         <v>1.367136085871659</v>
       </c>
       <c r="N95" s="132" t="n">
-        <v>26.24432748303784</v>
+        <v>26.24432748303783</v>
       </c>
       <c r="P95" s="130" t="n">
         <v>27.65663487526179</v>
@@ -33063,7 +33063,7 @@
         <v>0</v>
       </c>
       <c r="S95" s="131" t="n">
-        <v>1.446478003178301</v>
+        <v>1.4464780031783</v>
       </c>
       <c r="T95" s="132" t="n">
         <v>29.10311287844009</v>
@@ -33078,7 +33078,7 @@
         <v>0</v>
       </c>
       <c r="Y95" s="131" t="n">
-        <v>1.539423073904819</v>
+        <v>1.539423073904818</v>
       </c>
       <c r="Z95" s="132" t="n">
         <v>32.59117747634145</v>
@@ -33136,7 +33136,7 @@
         <v>26.57911917875575</v>
       </c>
       <c r="V96" s="130" t="n">
-        <v>28.06187153348852</v>
+        <v>28.06187153348851</v>
       </c>
       <c r="W96" s="131" t="n">
         <v>0</v>
@@ -33148,7 +33148,7 @@
         <v>0</v>
       </c>
       <c r="Z96" s="132" t="n">
-        <v>28.06187153348852</v>
+        <v>28.06187153348851</v>
       </c>
     </row>
     <row r="97">
@@ -33173,10 +33173,10 @@
         <v>9704</v>
       </c>
       <c r="J97" s="130" t="n">
-        <v>8521.815565172985</v>
+        <v>8521.815565172983</v>
       </c>
       <c r="K97" s="131" t="n">
-        <v>6628.085294105205</v>
+        <v>6628.085294105206</v>
       </c>
       <c r="L97" s="131" t="n">
         <v>81.12125915531615</v>
@@ -33188,10 +33188,10 @@
         <v>15231.02211843351</v>
       </c>
       <c r="P97" s="130" t="n">
-        <v>8787.458946566276</v>
+        <v>8787.458946566274</v>
       </c>
       <c r="Q97" s="131" t="n">
-        <v>6924.377261876311</v>
+        <v>6924.377261876312</v>
       </c>
       <c r="R97" s="131" t="n">
         <v>85.73780046159801</v>
@@ -33203,7 +33203,7 @@
         <v>15797.57400890418</v>
       </c>
       <c r="V97" s="130" t="n">
-        <v>9058.982559296477</v>
+        <v>9058.982559296473</v>
       </c>
       <c r="W97" s="131" t="n">
         <v>7214.103405258798</v>
@@ -33215,7 +33215,7 @@
         <v>0</v>
       </c>
       <c r="Z97" s="132" t="n">
-        <v>16363.1543764469</v>
+        <v>16363.15437644689</v>
       </c>
     </row>
     <row r="98">
@@ -33240,13 +33240,13 @@
         <v>976</v>
       </c>
       <c r="J98" s="130" t="n">
-        <v>351.9287478386029</v>
+        <v>351.9287478386028</v>
       </c>
       <c r="K98" s="131" t="n">
-        <v>695.26532200108</v>
+        <v>695.2653220010801</v>
       </c>
       <c r="L98" s="131" t="n">
-        <v>4.363987808065344</v>
+        <v>4.363987808065345</v>
       </c>
       <c r="M98" s="131" t="n">
         <v>0</v>
@@ -33255,10 +33255,10 @@
         <v>1051.558057647748</v>
       </c>
       <c r="P98" s="130" t="n">
-        <v>344.867797743876</v>
+        <v>344.8677977438759</v>
       </c>
       <c r="Q98" s="131" t="n">
-        <v>695.6708181072372</v>
+        <v>695.6708181072373</v>
       </c>
       <c r="R98" s="131" t="n">
         <v>4.376881306996877</v>
@@ -33270,10 +33270,10 @@
         <v>1044.91549715811</v>
       </c>
       <c r="V98" s="130" t="n">
-        <v>337.2252462051625</v>
+        <v>337.2252462051626</v>
       </c>
       <c r="W98" s="131" t="n">
-        <v>693.7423997998152</v>
+        <v>693.7423997998151</v>
       </c>
       <c r="X98" s="131" t="n">
         <v>4.349920807420687</v>
@@ -33328,10 +33328,10 @@
         <v>2604.95332839858</v>
       </c>
       <c r="R99" s="131" t="n">
-        <v>42.03577551248054</v>
+        <v>42.03577551247963</v>
       </c>
       <c r="S99" s="131" t="n">
-        <v>5099.728555144816</v>
+        <v>5099.728555144814</v>
       </c>
       <c r="T99" s="132" t="n">
         <v>10943.97587903814</v>
@@ -33346,7 +33346,7 @@
         <v>51.03255827472276</v>
       </c>
       <c r="Y99" s="131" t="n">
-        <v>5541.410161234373</v>
+        <v>5541.410161234372</v>
       </c>
       <c r="Z99" s="132" t="n">
         <v>12535.77328412354</v>
@@ -33398,10 +33398,10 @@
         <v>0</v>
       </c>
       <c r="S100" s="134" t="n">
-        <v>5099.725056957099</v>
+        <v>5099.725056957098</v>
       </c>
       <c r="T100" s="135" t="n">
-        <v>5099.725056957099</v>
+        <v>5099.725056957098</v>
       </c>
       <c r="V100" s="133" t="n">
         <v>0</v>
@@ -33615,10 +33615,10 @@
         <v>264737.8059749066</v>
       </c>
       <c r="X103" s="140" t="n">
-        <v>4142.034055145594</v>
+        <v>4142.034055145593</v>
       </c>
       <c r="Y103" s="140" t="n">
-        <v>507.7439456670622</v>
+        <v>507.7439456670623</v>
       </c>
       <c r="Z103" s="141" t="n">
         <v>545672.9854099642</v>
@@ -33667,10 +33667,10 @@
         <v>273437.7993541604</v>
       </c>
       <c r="R104" s="143" t="n">
-        <v>4247.739981535529</v>
+        <v>4247.739981535528</v>
       </c>
       <c r="S104" s="143" t="n">
-        <v>5630.618451034226</v>
+        <v>5630.618451034225</v>
       </c>
       <c r="T104" s="144" t="n">
         <v>574767.6038082013</v>
@@ -33682,13 +33682,13 @@
         <v>275824.1403448745</v>
       </c>
       <c r="X104" s="143" t="n">
-        <v>4287.484946119356</v>
+        <v>4287.484946119355</v>
       </c>
       <c r="Y104" s="143" t="n">
         <v>6050.69352997534</v>
       </c>
       <c r="Z104" s="144" t="n">
-        <v>581216.5896308239</v>
+        <v>581216.5896308238</v>
       </c>
     </row>
     <row r="105" ht="30.3" customHeight="1" thickBot="1"/>
